--- a/03_DEP/sensitivity_analysis/c_data/06_sensitivity_supplementary.xlsx
+++ b/03_DEP/sensitivity_analysis/c_data/06_sensitivity_supplementary.xlsx
@@ -61,28 +61,28 @@
     <t xml:space="preserve">vsn_bpca</t>
   </si>
   <si>
-    <t xml:space="preserve">cycloess_mix_bpca_MinDet</t>
+    <t xml:space="preserve">cycloess_mix_bpca_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">mix_bpca_MinDet</t>
+    <t xml:space="preserve">mix_bpca_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr_mix_bpca_MinDet</t>
+    <t xml:space="preserve">rlr_mix_bpca_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">vsn_mix_bpca_MinDet</t>
+    <t xml:space="preserve">vsn_mix_bpca_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">cycloess_mix_bpca_MinProb</t>
+    <t xml:space="preserve">cycloess_mix_RF_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">mix_bpca_MinProb</t>
+    <t xml:space="preserve">mix_RF_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr_mix_bpca_MinProb</t>
+    <t xml:space="preserve">rlr_mix_RF_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">vsn_mix_bpca_MinProb</t>
+    <t xml:space="preserve">vsn_mix_RF_QRILC</t>
   </si>
   <si>
     <t xml:space="preserve">Mean Spearman rho</t>
@@ -668,80 +668,80 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8914</v>
+        <v>0.9169</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8854</v>
+        <v>0.9148</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9208</v>
+        <v>0.9428</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8946</v>
+        <v>0.9103</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8649</v>
+        <v>0.8997</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8901</v>
+        <v>0.9168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8843</v>
+        <v>0.9153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.922</v>
+        <v>0.9462</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8928</v>
+        <v>0.9089</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8614</v>
+        <v>0.8969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8867</v>
+        <v>0.9161</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8772</v>
+        <v>0.916</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9196</v>
+        <v>0.9446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8931</v>
+        <v>0.9083</v>
       </c>
       <c r="H4" t="n">
-        <v>0.857</v>
+        <v>0.8954</v>
       </c>
     </row>
     <row r="5">
@@ -755,227 +755,227 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8839</v>
+        <v>0.9142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8749</v>
+        <v>0.9115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9226</v>
+        <v>0.9496</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8765</v>
+        <v>0.8946</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8616</v>
+        <v>0.9011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>0.883</v>
+        <v>0.9141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8766</v>
+        <v>0.9114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9242</v>
+        <v>0.9429</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8655</v>
+        <v>0.9092</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8657</v>
+        <v>0.8928</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8821</v>
+        <v>0.9137</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8834</v>
+        <v>0.9138</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9159</v>
+        <v>0.9443</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8727</v>
+        <v>0.8982</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8565</v>
+        <v>0.8986</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8816</v>
+        <v>0.9129</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8744</v>
+        <v>0.9091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9247</v>
+        <v>0.9428</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8661</v>
+        <v>0.9069</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8611</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8809</v>
+        <v>0.912</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8804</v>
+        <v>0.9121</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9154</v>
+        <v>0.9455</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8737</v>
+        <v>0.8963</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8542</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641</v>
+        <v>0.9057</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8614</v>
+        <v>0.9062</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9125</v>
+        <v>0.9509</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8403</v>
+        <v>0.8665</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8423</v>
+        <v>0.8993</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7767</v>
+        <v>0.9041</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7557</v>
+        <v>0.9034</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8114</v>
+        <v>0.9516</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8231</v>
+        <v>0.8677</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7165</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7702</v>
+        <v>0.9035</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7486</v>
+        <v>0.8974</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8101</v>
+        <v>0.9442</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8116</v>
+        <v>0.8859</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7104</v>
+        <v>0.8866</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7668</v>
+        <v>0.9001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7503</v>
+        <v>0.8936</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8121</v>
+        <v>0.9393</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8074</v>
+        <v>0.8844</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6973</v>
+        <v>0.8832</v>
       </c>
     </row>
   </sheetData>
@@ -1025,36 +1025,36 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="D3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E3" t="n">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>154</v>
+        <v>478</v>
       </c>
       <c r="D4" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="E4" t="n">
-        <v>285</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5">
@@ -1093,36 +1093,36 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="D7" t="n">
         <v>181</v>
       </c>
       <c r="E7" t="n">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>148</v>
+        <v>501</v>
       </c>
       <c r="D8" t="n">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="E8" t="n">
-        <v>272</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9">
@@ -1161,36 +1161,36 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="D11" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E11" t="n">
-        <v>776</v>
+        <v>760</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>554</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>221</v>
       </c>
       <c r="E12" t="n">
-        <v>298</v>
+        <v>775</v>
       </c>
     </row>
     <row r="13">
@@ -1229,7 +1229,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -1238,15 +1238,15 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -1306,15 +1306,15 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -1374,15 +1374,15 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -1450,19 +1450,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1501,36 +1501,36 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1569,36 +1569,36 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1637,36 +1637,36 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D39" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E40" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41">
@@ -1705,36 +1705,36 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
         <v>35</v>
       </c>
       <c r="C43" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D43" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E43" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
         <v>35</v>
       </c>
       <c r="C44" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="D44" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45">
@@ -1773,36 +1773,36 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
         <v>35</v>
       </c>
       <c r="C47" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E47" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E48" t="n">
-        <v>40</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49">
@@ -1875,7 +1875,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
@@ -1884,18 +1884,18 @@
         <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="E3" t="n">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F3" t="n">
-        <v>885</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
@@ -1904,13 +1904,13 @@
         <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>312</v>
+        <v>591</v>
       </c>
       <c r="E4" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="F4" t="n">
-        <v>564</v>
+        <v>863</v>
       </c>
     </row>
     <row r="5">
@@ -1955,7 +1955,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -1964,18 +1964,18 @@
         <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="E7" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F7" t="n">
-        <v>901</v>
+        <v>893</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
@@ -1984,13 +1984,13 @@
         <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>627</v>
       </c>
       <c r="E8" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F8" t="n">
-        <v>573</v>
+        <v>879</v>
       </c>
     </row>
     <row r="9">
@@ -2035,7 +2035,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
@@ -2044,18 +2044,18 @@
         <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="E11" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F11" t="n">
-        <v>954</v>
+        <v>941</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -2064,13 +2064,13 @@
         <v>37</v>
       </c>
       <c r="D12" t="n">
-        <v>311</v>
+        <v>671</v>
       </c>
       <c r="E12" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F12" t="n">
-        <v>577</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13">
@@ -2115,7 +2115,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
@@ -2124,18 +2124,18 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="E15" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F15" t="n">
-        <v>845</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
@@ -2144,13 +2144,13 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>217</v>
+        <v>571</v>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="F16" t="n">
-        <v>403</v>
+        <v>826</v>
       </c>
     </row>
     <row r="17">
@@ -2195,7 +2195,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
@@ -2204,18 +2204,18 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E19" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F19" t="n">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
         <v>32</v>
@@ -2224,13 +2224,13 @@
         <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>222</v>
+        <v>594</v>
       </c>
       <c r="E20" t="n">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="F20" t="n">
-        <v>394</v>
+        <v>825</v>
       </c>
     </row>
     <row r="21">
@@ -2275,7 +2275,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -2284,18 +2284,18 @@
         <v>38</v>
       </c>
       <c r="D23" t="n">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="E23" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F23" t="n">
-        <v>926</v>
+        <v>906</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
@@ -2304,13 +2304,13 @@
         <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>215</v>
+        <v>647</v>
       </c>
       <c r="E24" t="n">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="F24" t="n">
-        <v>418</v>
+        <v>914</v>
       </c>
     </row>
     <row r="25">
@@ -2355,7 +2355,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
@@ -2364,18 +2364,18 @@
         <v>39</v>
       </c>
       <c r="D27" t="n">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="E27" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F27" t="n">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
@@ -2384,13 +2384,13 @@
         <v>39</v>
       </c>
       <c r="D28" t="n">
-        <v>154</v>
+        <v>478</v>
       </c>
       <c r="E28" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="F28" t="n">
-        <v>285</v>
+        <v>667</v>
       </c>
     </row>
     <row r="29">
@@ -2435,7 +2435,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
@@ -2444,18 +2444,18 @@
         <v>39</v>
       </c>
       <c r="D31" t="n">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="E31" t="n">
         <v>181</v>
       </c>
       <c r="F31" t="n">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
@@ -2464,13 +2464,13 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>148</v>
+        <v>501</v>
       </c>
       <c r="E32" t="n">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="F32" t="n">
-        <v>272</v>
+        <v>677</v>
       </c>
     </row>
     <row r="33">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>32</v>
@@ -2524,18 +2524,18 @@
         <v>39</v>
       </c>
       <c r="D35" t="n">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="E35" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F35" t="n">
-        <v>776</v>
+        <v>760</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>32</v>
@@ -2544,13 +2544,13 @@
         <v>39</v>
       </c>
       <c r="D36" t="n">
-        <v>143</v>
+        <v>554</v>
       </c>
       <c r="E36" t="n">
-        <v>155</v>
+        <v>221</v>
       </c>
       <c r="F36" t="n">
-        <v>298</v>
+        <v>775</v>
       </c>
     </row>
     <row r="37">
@@ -2595,7 +2595,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
         <v>32</v>
@@ -2604,18 +2604,18 @@
         <v>40</v>
       </c>
       <c r="D39" t="n">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="E39" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F39" t="n">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
         <v>32</v>
@@ -2624,13 +2624,13 @@
         <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>166</v>
+        <v>300</v>
       </c>
       <c r="E40" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F40" t="n">
-        <v>279</v>
+        <v>414</v>
       </c>
     </row>
     <row r="41">
@@ -2675,7 +2675,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
         <v>32</v>
@@ -2684,18 +2684,18 @@
         <v>40</v>
       </c>
       <c r="D43" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="E43" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
         <v>32</v>
@@ -2704,13 +2704,13 @@
         <v>40</v>
       </c>
       <c r="D44" t="n">
-        <v>168</v>
+        <v>314</v>
       </c>
       <c r="E44" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="F44" t="n">
-        <v>289</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
         <v>32</v>
@@ -2764,18 +2764,18 @@
         <v>40</v>
       </c>
       <c r="D47" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E47" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F47" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
         <v>32</v>
@@ -2784,13 +2784,13 @@
         <v>40</v>
       </c>
       <c r="D48" t="n">
-        <v>174</v>
+        <v>345</v>
       </c>
       <c r="E48" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F48" t="n">
-        <v>297</v>
+        <v>473</v>
       </c>
     </row>
     <row r="49">
@@ -2835,7 +2835,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B51" t="s">
         <v>33</v>
@@ -2844,18 +2844,18 @@
         <v>37</v>
       </c>
       <c r="D51" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E51" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F51" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
         <v>33</v>
@@ -2864,13 +2864,13 @@
         <v>37</v>
       </c>
       <c r="D52" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F52" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B55" t="s">
         <v>33</v>
@@ -2924,18 +2924,18 @@
         <v>37</v>
       </c>
       <c r="D55" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E55" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F55" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
         <v>33</v>
@@ -2944,13 +2944,13 @@
         <v>37</v>
       </c>
       <c r="D56" t="n">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E56" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F56" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57">
@@ -2995,7 +2995,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>33</v>
@@ -3004,10 +3004,10 @@
         <v>37</v>
       </c>
       <c r="D59" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E59" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F59" t="n">
         <v>172</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
         <v>33</v>
@@ -3024,13 +3024,13 @@
         <v>37</v>
       </c>
       <c r="D60" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="E60" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F60" t="n">
-        <v>185</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B63" t="s">
         <v>33</v>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
         <v>33</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3155,7 +3155,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B67" t="s">
         <v>33</v>
@@ -3167,15 +3167,15 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
         <v>33</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B71" t="s">
         <v>33</v>
@@ -3247,15 +3247,15 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
         <v>33</v>
@@ -3267,10 +3267,10 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3315,7 +3315,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B75" t="s">
         <v>33</v>
@@ -3327,15 +3327,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
         <v>33</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B79" t="s">
         <v>33</v>
@@ -3407,15 +3407,15 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
         <v>33</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
         <v>33</v>
@@ -3487,15 +3487,15 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
         <v>33</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B87" t="s">
         <v>33</v>
@@ -3564,18 +3564,18 @@
         <v>40</v>
       </c>
       <c r="D87" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E87" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B88" t="s">
         <v>33</v>
@@ -3584,13 +3584,13 @@
         <v>40</v>
       </c>
       <c r="D88" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E88" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B91" t="s">
         <v>33</v>
@@ -3644,18 +3644,18 @@
         <v>40</v>
       </c>
       <c r="D91" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F91" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B92" t="s">
         <v>33</v>
@@ -3664,13 +3664,13 @@
         <v>40</v>
       </c>
       <c r="D92" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="E92" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>131</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93">
@@ -3715,7 +3715,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B95" t="s">
         <v>33</v>
@@ -3724,18 +3724,18 @@
         <v>40</v>
       </c>
       <c r="D95" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E95" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
         <v>33</v>
@@ -3744,13 +3744,13 @@
         <v>40</v>
       </c>
       <c r="D96" t="n">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E96" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F96" t="n">
-        <v>141</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
@@ -3795,7 +3795,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B99" t="s">
         <v>34</v>
@@ -3804,18 +3804,18 @@
         <v>37</v>
       </c>
       <c r="D99" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E99" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F99" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B100" t="s">
         <v>34</v>
@@ -3824,13 +3824,13 @@
         <v>37</v>
       </c>
       <c r="D100" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E100" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F100" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="101">
@@ -3875,7 +3875,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
         <v>34</v>
@@ -3884,18 +3884,18 @@
         <v>37</v>
       </c>
       <c r="D103" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E103" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F103" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B104" t="s">
         <v>34</v>
@@ -3904,13 +3904,13 @@
         <v>37</v>
       </c>
       <c r="D104" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E104" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F104" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="105">
@@ -3955,7 +3955,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B107" t="s">
         <v>34</v>
@@ -3964,18 +3964,18 @@
         <v>37</v>
       </c>
       <c r="D107" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E107" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F107" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
         <v>34</v>
@@ -3984,13 +3984,13 @@
         <v>37</v>
       </c>
       <c r="D108" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E108" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F108" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="109">
@@ -4035,7 +4035,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B111" t="s">
         <v>34</v>
@@ -4047,15 +4047,15 @@
         <v>2</v>
       </c>
       <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
         <v>4</v>
-      </c>
-      <c r="F111" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B112" t="s">
         <v>34</v>
@@ -4064,13 +4064,13 @@
         <v>38</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
@@ -4115,7 +4115,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B115" t="s">
         <v>34</v>
@@ -4124,18 +4124,18 @@
         <v>38</v>
       </c>
       <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
         <v>2</v>
       </c>
-      <c r="E115" t="n">
-        <v>4</v>
-      </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B116" t="s">
         <v>34</v>
@@ -4144,13 +4144,13 @@
         <v>38</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
@@ -4195,7 +4195,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B119" t="s">
         <v>34</v>
@@ -4204,18 +4204,18 @@
         <v>38</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
         <v>34</v>
@@ -4224,13 +4224,13 @@
         <v>38</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -4275,7 +4275,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B123" t="s">
         <v>34</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B124" t="s">
         <v>34</v>
@@ -4304,13 +4304,13 @@
         <v>39</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -4355,7 +4355,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B127" t="s">
         <v>34</v>
@@ -4364,18 +4364,18 @@
         <v>39</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B128" t="s">
         <v>34</v>
@@ -4384,13 +4384,13 @@
         <v>39</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
@@ -4435,7 +4435,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B131" t="s">
         <v>34</v>
@@ -4444,18 +4444,18 @@
         <v>39</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
         <v>34</v>
@@ -4464,13 +4464,13 @@
         <v>39</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4515,7 +4515,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B135" t="s">
         <v>34</v>
@@ -4535,7 +4535,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B136" t="s">
         <v>34</v>
@@ -4544,13 +4544,13 @@
         <v>40</v>
       </c>
       <c r="D136" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E136" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F136" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137">
@@ -4595,7 +4595,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B139" t="s">
         <v>34</v>
@@ -4604,18 +4604,18 @@
         <v>40</v>
       </c>
       <c r="D139" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E139" t="n">
         <v>9</v>
       </c>
       <c r="F139" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B140" t="s">
         <v>34</v>
@@ -4624,13 +4624,13 @@
         <v>40</v>
       </c>
       <c r="D140" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E140" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F140" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141">
@@ -4675,7 +4675,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B143" t="s">
         <v>34</v>
@@ -4684,18 +4684,18 @@
         <v>40</v>
       </c>
       <c r="D143" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F143" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
         <v>34</v>
@@ -4704,13 +4704,13 @@
         <v>40</v>
       </c>
       <c r="D144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E144" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F144" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B147" t="s">
         <v>35</v>
@@ -4764,10 +4764,10 @@
         <v>37</v>
       </c>
       <c r="D147" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E147" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F147" t="n">
         <v>472</v>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B148" t="s">
         <v>35</v>
@@ -4784,13 +4784,13 @@
         <v>37</v>
       </c>
       <c r="D148" t="n">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="E148" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F148" t="n">
-        <v>380</v>
+        <v>457</v>
       </c>
     </row>
     <row r="149">
@@ -4835,7 +4835,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
         <v>35</v>
@@ -4844,18 +4844,18 @@
         <v>37</v>
       </c>
       <c r="D151" t="n">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="E151" t="n">
         <v>175</v>
       </c>
       <c r="F151" t="n">
-        <v>470</v>
+        <v>458</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B152" t="s">
         <v>35</v>
@@ -4864,13 +4864,13 @@
         <v>37</v>
       </c>
       <c r="D152" t="n">
-        <v>206</v>
+        <v>286</v>
       </c>
       <c r="E152" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F152" t="n">
-        <v>373</v>
+        <v>456</v>
       </c>
     </row>
     <row r="153">
@@ -4915,7 +4915,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B155" t="s">
         <v>35</v>
@@ -4924,18 +4924,18 @@
         <v>37</v>
       </c>
       <c r="D155" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E155" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F155" t="n">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B156" t="s">
         <v>35</v>
@@ -4944,13 +4944,13 @@
         <v>37</v>
       </c>
       <c r="D156" t="n">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="E156" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="F156" t="n">
-        <v>389</v>
+        <v>466</v>
       </c>
     </row>
     <row r="157">
@@ -4995,7 +4995,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B159" t="s">
         <v>35</v>
@@ -5004,18 +5004,18 @@
         <v>38</v>
       </c>
       <c r="D159" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E159" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F159" t="n">
-        <v>258</v>
+        <v>236</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B160" t="s">
         <v>35</v>
@@ -5024,13 +5024,13 @@
         <v>38</v>
       </c>
       <c r="D160" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E160" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="F160" t="n">
-        <v>98</v>
+        <v>242</v>
       </c>
     </row>
     <row r="161">
@@ -5075,7 +5075,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B163" t="s">
         <v>35</v>
@@ -5084,18 +5084,18 @@
         <v>38</v>
       </c>
       <c r="D163" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="E163" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F163" t="n">
-        <v>256</v>
+        <v>224</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B164" t="s">
         <v>35</v>
@@ -5104,13 +5104,13 @@
         <v>38</v>
       </c>
       <c r="D164" t="n">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="E164" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="F164" t="n">
-        <v>97</v>
+        <v>226</v>
       </c>
     </row>
     <row r="165">
@@ -5155,7 +5155,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B167" t="s">
         <v>35</v>
@@ -5164,18 +5164,18 @@
         <v>38</v>
       </c>
       <c r="D167" t="n">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="E167" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F167" t="n">
-        <v>281</v>
+        <v>249</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B168" t="s">
         <v>35</v>
@@ -5184,13 +5184,13 @@
         <v>38</v>
       </c>
       <c r="D168" t="n">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="E168" t="n">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>139</v>
+        <v>252</v>
       </c>
     </row>
     <row r="169">
@@ -5235,7 +5235,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B171" t="s">
         <v>35</v>
@@ -5244,18 +5244,18 @@
         <v>39</v>
       </c>
       <c r="D171" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E171" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F171" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B172" t="s">
         <v>35</v>
@@ -5264,13 +5264,13 @@
         <v>39</v>
       </c>
       <c r="D172" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="E172" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F172" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
     </row>
     <row r="173">
@@ -5315,7 +5315,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B175" t="s">
         <v>35</v>
@@ -5324,18 +5324,18 @@
         <v>39</v>
       </c>
       <c r="D175" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E175" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F175" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B176" t="s">
         <v>35</v>
@@ -5344,13 +5344,13 @@
         <v>39</v>
       </c>
       <c r="D176" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E176" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F176" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="177">
@@ -5395,7 +5395,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B179" t="s">
         <v>35</v>
@@ -5404,18 +5404,18 @@
         <v>39</v>
       </c>
       <c r="D179" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E179" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F179" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B180" t="s">
         <v>35</v>
@@ -5424,13 +5424,13 @@
         <v>39</v>
       </c>
       <c r="D180" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E180" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="F180" t="n">
-        <v>40</v>
+        <v>124</v>
       </c>
     </row>
     <row r="181">
@@ -5475,7 +5475,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B183" t="s">
         <v>35</v>
@@ -5484,18 +5484,18 @@
         <v>40</v>
       </c>
       <c r="D183" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E183" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F183" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B184" t="s">
         <v>35</v>
@@ -5504,13 +5504,13 @@
         <v>40</v>
       </c>
       <c r="D184" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E184" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="F184" t="n">
-        <v>155</v>
+        <v>100</v>
       </c>
     </row>
     <row r="185">
@@ -5555,7 +5555,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B187" t="s">
         <v>35</v>
@@ -5564,18 +5564,18 @@
         <v>40</v>
       </c>
       <c r="D187" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E187" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F187" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B188" t="s">
         <v>35</v>
@@ -5584,13 +5584,13 @@
         <v>40</v>
       </c>
       <c r="D188" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E188" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F188" t="n">
-        <v>150</v>
+        <v>97</v>
       </c>
     </row>
     <row r="189">
@@ -5635,7 +5635,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B191" t="s">
         <v>35</v>
@@ -5644,18 +5644,18 @@
         <v>40</v>
       </c>
       <c r="D191" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E191" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F191" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B192" t="s">
         <v>35</v>
@@ -5664,13 +5664,13 @@
         <v>40</v>
       </c>
       <c r="D192" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="E192" t="n">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="F192" t="n">
-        <v>175</v>
+        <v>101</v>
       </c>
     </row>
     <row r="193">
@@ -5723,13 +5723,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.998627465695237</v>
+        <v>0.998355715707329</v>
       </c>
     </row>
     <row r="3">
@@ -5737,13 +5737,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.998355715707329</v>
+        <v>0.998322547706496</v>
       </c>
     </row>
     <row r="4">
@@ -5751,13 +5751,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0.998322547706496</v>
+        <v>0.992826254162618</v>
       </c>
     </row>
     <row r="5">
@@ -5765,13 +5765,13 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.966395042537641</v>
+        <v>0.99226723409611</v>
       </c>
     </row>
     <row r="6">
@@ -5779,13 +5779,13 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0.964281419832198</v>
+        <v>0.99101150559939</v>
       </c>
     </row>
     <row r="7">
@@ -5793,13 +5793,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>0.959226506382697</v>
+        <v>0.990885649222845</v>
       </c>
     </row>
     <row r="8">
@@ -5807,13 +5807,13 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>0.953762356597789</v>
+        <v>0.990520538243959</v>
       </c>
     </row>
     <row r="9">
@@ -5821,13 +5821,13 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>0.953621590243896</v>
+        <v>0.990060537182612</v>
       </c>
     </row>
     <row r="10">
@@ -5835,13 +5835,13 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.952876345787086</v>
+        <v>0.989709392156393</v>
       </c>
     </row>
     <row r="11">
@@ -5849,13 +5849,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>0.952451554353873</v>
+        <v>0.960180273749328</v>
       </c>
     </row>
     <row r="12">
@@ -5863,13 +5863,13 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>0.952089438771583</v>
+        <v>0.959754925833271</v>
       </c>
     </row>
     <row r="13">
@@ -5877,13 +5877,13 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
       <c r="D13" t="n">
-        <v>0.95023403495558</v>
+        <v>0.959226506382697</v>
       </c>
     </row>
     <row r="14">
@@ -5891,13 +5891,13 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>0.940731696573022</v>
+        <v>0.958809190891762</v>
       </c>
     </row>
     <row r="15">
@@ -5905,13 +5905,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>0.940029977581778</v>
+        <v>0.958642940702152</v>
       </c>
     </row>
     <row r="16">
@@ -5919,13 +5919,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>0.908565216795165</v>
+        <v>0.956600571656048</v>
       </c>
     </row>
     <row r="17">
@@ -5933,13 +5933,13 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>0.905774411355432</v>
+        <v>0.95635237042836</v>
       </c>
     </row>
     <row r="18">
@@ -5947,13 +5947,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>0.90559529292107</v>
+        <v>0.955675463795456</v>
       </c>
     </row>
     <row r="19">
@@ -5961,13 +5961,13 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>0.905136238672441</v>
+        <v>0.955076540828136</v>
       </c>
     </row>
     <row r="20">
@@ -5975,13 +5975,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.895117009106466</v>
+        <v>0.953762356597789</v>
       </c>
     </row>
     <row r="21">
@@ -5989,13 +5989,13 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>0.883517343284656</v>
+        <v>0.953621590243896</v>
       </c>
     </row>
     <row r="22">
@@ -6003,13 +6003,13 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.883217634269432</v>
+        <v>0.952876345787086</v>
       </c>
     </row>
     <row r="23">
@@ -6017,13 +6017,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.880990358860025</v>
+        <v>0.952451554353873</v>
       </c>
     </row>
     <row r="24">
@@ -6031,13 +6031,13 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.875679030135917</v>
+        <v>0.952089438771583</v>
       </c>
     </row>
     <row r="25">
@@ -6045,13 +6045,13 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.874304843015283</v>
+        <v>0.95023403495558</v>
       </c>
     </row>
     <row r="26">
@@ -6059,13 +6059,13 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>0.873910093220657</v>
+        <v>0.940731696573022</v>
       </c>
     </row>
     <row r="27">
@@ -6073,13 +6073,13 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>0.872522485345204</v>
+        <v>0.940029977581778</v>
       </c>
     </row>
     <row r="28">
@@ -6087,13 +6087,13 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.867105986797028</v>
+        <v>0.908565216795165</v>
       </c>
     </row>
     <row r="29">
@@ -6101,13 +6101,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.865098290933449</v>
+        <v>0.905774411355432</v>
       </c>
     </row>
     <row r="30">
@@ -6115,13 +6115,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.855570577854628</v>
+        <v>0.90559529292107</v>
       </c>
     </row>
     <row r="31">
@@ -6129,13 +6129,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.854589622274815</v>
+        <v>0.905136238672441</v>
       </c>
     </row>
     <row r="32">
@@ -6143,13 +6143,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.851913568664702</v>
+        <v>0.894666995888018</v>
       </c>
     </row>
     <row r="33">
@@ -6157,13 +6157,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>0.845140206950197</v>
+        <v>0.893446469497374</v>
       </c>
     </row>
     <row r="34">
@@ -6171,13 +6171,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.843974430525765</v>
+        <v>0.881184051008863</v>
       </c>
     </row>
     <row r="35">
@@ -6185,13 +6185,13 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.843397534667842</v>
+        <v>0.880100333618833</v>
       </c>
     </row>
     <row r="36">
@@ -6199,13 +6199,13 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>0.843045969017113</v>
+        <v>0.879200727226391</v>
       </c>
     </row>
     <row r="37">
@@ -6213,13 +6213,13 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>0.837099110581586</v>
+        <v>0.877739134392136</v>
       </c>
     </row>
     <row r="38">
@@ -6227,13 +6227,13 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>0.834196087197663</v>
+        <v>0.877147133571808</v>
       </c>
     </row>
     <row r="39">
@@ -6241,13 +6241,13 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>0.83413156730155</v>
+        <v>0.876124135982624</v>
       </c>
     </row>
     <row r="40">
@@ -6255,13 +6255,13 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.831016635131503</v>
+        <v>0.874313452795428</v>
       </c>
     </row>
     <row r="41">
@@ -6269,13 +6269,13 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.826374482336652</v>
+        <v>0.872677064384096</v>
       </c>
     </row>
     <row r="42">
@@ -6283,13 +6283,13 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.825317822635094</v>
+        <v>0.872656862856641</v>
       </c>
     </row>
     <row r="43">
@@ -6297,13 +6297,13 @@
         <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.824073939901132</v>
+        <v>0.87226516225345</v>
       </c>
     </row>
     <row r="44">
@@ -6314,10 +6314,10 @@
         <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>0.822573896147951</v>
+        <v>0.871063582960007</v>
       </c>
     </row>
     <row r="45">
@@ -6328,10 +6328,10 @@
         <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.822286189007166</v>
+        <v>0.870561261648872</v>
       </c>
     </row>
     <row r="46">
@@ -6339,13 +6339,13 @@
         <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.821341453422743</v>
+        <v>0.870029515133027</v>
       </c>
     </row>
     <row r="47">
@@ -6353,13 +6353,13 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>0.820925559324539</v>
+        <v>0.869524876487136</v>
       </c>
     </row>
     <row r="48">
@@ -6367,13 +6367,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>0.81823827183859</v>
+        <v>0.859471338222732</v>
       </c>
     </row>
     <row r="49">
@@ -6381,13 +6381,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D49" t="n">
-        <v>0.814944945922704</v>
+        <v>0.857643979977167</v>
       </c>
     </row>
     <row r="50">
@@ -6395,13 +6395,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>0.81145677746406</v>
+        <v>0.856748050087452</v>
       </c>
     </row>
     <row r="51">
@@ -6409,13 +6409,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D51" t="n">
-        <v>0.810757919022227</v>
+        <v>0.856325404693441</v>
       </c>
     </row>
     <row r="52">
@@ -6423,13 +6423,13 @@
         <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
-        <v>0.809393747049505</v>
+        <v>0.81985340696391</v>
       </c>
     </row>
     <row r="53">
@@ -6437,13 +6437,13 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D53" t="n">
-        <v>0.807533990144896</v>
+        <v>0.818482633431156</v>
       </c>
     </row>
     <row r="54">
@@ -6451,13 +6451,13 @@
         <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>0.807186067484468</v>
+        <v>0.817618393680632</v>
       </c>
     </row>
     <row r="55">
@@ -6465,13 +6465,13 @@
         <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>0.807090920674936</v>
+        <v>0.81635097596205</v>
       </c>
     </row>
     <row r="56">
@@ -6479,13 +6479,13 @@
         <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>0.80590404387403</v>
+        <v>0.816172905056224</v>
       </c>
     </row>
     <row r="57">
@@ -6493,13 +6493,13 @@
         <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>0.794501963101119</v>
+        <v>0.815410654830923</v>
       </c>
     </row>
     <row r="58">
@@ -6513,7 +6513,7 @@
         <v>10</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7937414723955</v>
+        <v>0.81490631763056</v>
       </c>
     </row>
     <row r="59">
@@ -6521,13 +6521,13 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>0.791249490341975</v>
+        <v>0.814293821941305</v>
       </c>
     </row>
     <row r="60">
@@ -6535,13 +6535,13 @@
         <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.789908765147484</v>
+        <v>0.812740054540192</v>
       </c>
     </row>
     <row r="61">
@@ -6549,13 +6549,13 @@
         <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>0.788258134060685</v>
+        <v>0.810989528196351</v>
       </c>
     </row>
     <row r="62">
@@ -6563,13 +6563,13 @@
         <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>0.765487958169768</v>
+        <v>0.808834290182036</v>
       </c>
     </row>
     <row r="63">
@@ -6580,10 +6580,10 @@
         <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>0.763944243263302</v>
+        <v>0.807040853191161</v>
       </c>
     </row>
     <row r="64">
@@ -6597,7 +6597,7 @@
         <v>12</v>
       </c>
       <c r="D64" t="n">
-        <v>0.763738380712784</v>
+        <v>0.762800157229677</v>
       </c>
     </row>
     <row r="65">
@@ -6605,13 +6605,13 @@
         <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D65" t="n">
-        <v>0.762955723816148</v>
+        <v>0.76130327810727</v>
       </c>
     </row>
     <row r="66">
@@ -6619,13 +6619,13 @@
         <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>0.762530369638455</v>
+        <v>0.760330108434314</v>
       </c>
     </row>
     <row r="67">
@@ -6633,13 +6633,13 @@
         <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67" t="s">
         <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>0.761876698683976</v>
+        <v>0.758868050269039</v>
       </c>
     </row>
     <row r="68">
@@ -6661,13 +6661,13 @@
         <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>0.997900231790106</v>
+        <v>0.997673664558614</v>
       </c>
     </row>
     <row r="70">
@@ -6675,13 +6675,13 @@
         <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>0.997673664558614</v>
+        <v>0.975376717931088</v>
       </c>
     </row>
     <row r="71">
@@ -6689,13 +6689,13 @@
         <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>0.977659290929222</v>
+        <v>0.971935531215164</v>
       </c>
     </row>
     <row r="72">
@@ -6703,13 +6703,13 @@
         <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>0.975609334032758</v>
+        <v>0.968703363296826</v>
       </c>
     </row>
     <row r="73">
@@ -6717,13 +6717,13 @@
         <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D73" t="n">
-        <v>0.975376717931088</v>
+        <v>0.965178599544435</v>
       </c>
     </row>
     <row r="74">
@@ -6731,13 +6731,13 @@
         <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>0.971935531215164</v>
+        <v>0.963284345738104</v>
       </c>
     </row>
     <row r="75">
@@ -6745,13 +6745,13 @@
         <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D75" t="n">
-        <v>0.968703363296826</v>
+        <v>0.959915346439877</v>
       </c>
     </row>
     <row r="76">
@@ -6759,13 +6759,13 @@
         <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C76" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D76" t="n">
-        <v>0.963284345738104</v>
+        <v>0.959273116746479</v>
       </c>
     </row>
     <row r="77">
@@ -6773,13 +6773,13 @@
         <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
-        <v>0.953016028192698</v>
+        <v>0.958635392926261</v>
       </c>
     </row>
     <row r="78">
@@ -6787,13 +6787,13 @@
         <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D78" t="n">
-        <v>0.952855888779202</v>
+        <v>0.957899957530455</v>
       </c>
     </row>
     <row r="79">
@@ -6801,13 +6801,13 @@
         <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D79" t="n">
-        <v>0.952507009312699</v>
+        <v>0.957122084523631</v>
       </c>
     </row>
     <row r="80">
@@ -6815,13 +6815,13 @@
         <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D80" t="n">
-        <v>0.95223357778627</v>
+        <v>0.956952278977168</v>
       </c>
     </row>
     <row r="81">
@@ -6829,13 +6829,13 @@
         <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>0.949338821647445</v>
+        <v>0.953016028192698</v>
       </c>
     </row>
     <row r="82">
@@ -6843,13 +6843,13 @@
         <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>0.929959267448748</v>
+        <v>0.952855888779202</v>
       </c>
     </row>
     <row r="83">
@@ -6857,13 +6857,13 @@
         <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>0.926007329405816</v>
+        <v>0.952507009312699</v>
       </c>
     </row>
     <row r="84">
@@ -6871,13 +6871,13 @@
         <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
         <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>0.925122141838942</v>
+        <v>0.95223357778627</v>
       </c>
     </row>
     <row r="85">
@@ -6888,10 +6888,10 @@
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>0.921402977513174</v>
+        <v>0.949338821647445</v>
       </c>
     </row>
     <row r="86">
@@ -6902,10 +6902,10 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D86" t="n">
-        <v>0.892176203059842</v>
+        <v>0.941793623682258</v>
       </c>
     </row>
     <row r="87">
@@ -6913,13 +6913,13 @@
         <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D87" t="n">
-        <v>0.876564815210516</v>
+        <v>0.937102335950228</v>
       </c>
     </row>
     <row r="88">
@@ -6927,13 +6927,13 @@
         <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D88" t="n">
-        <v>0.873321831334384</v>
+        <v>0.936460637243553</v>
       </c>
     </row>
     <row r="89">
@@ -6941,13 +6941,13 @@
         <v>33</v>
       </c>
       <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s">
         <v>14</v>
       </c>
-      <c r="C89" t="s">
-        <v>13</v>
-      </c>
       <c r="D89" t="n">
-        <v>0.872990498124092</v>
+        <v>0.936145391428165</v>
       </c>
     </row>
     <row r="90">
@@ -6955,13 +6955,13 @@
         <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D90" t="n">
-        <v>0.872182057063227</v>
+        <v>0.935391340188886</v>
       </c>
     </row>
     <row r="91">
@@ -6969,13 +6969,13 @@
         <v>33</v>
       </c>
       <c r="B91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" t="s">
         <v>16</v>
       </c>
-      <c r="C91" t="s">
-        <v>12</v>
-      </c>
       <c r="D91" t="n">
-        <v>0.871033421324972</v>
+        <v>0.934093328117391</v>
       </c>
     </row>
     <row r="92">
@@ -6983,13 +6983,13 @@
         <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D92" t="n">
-        <v>0.869862388961086</v>
+        <v>0.933557099153161</v>
       </c>
     </row>
     <row r="93">
@@ -6997,13 +6997,13 @@
         <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
         <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>0.868203207160854</v>
+        <v>0.929959267448748</v>
       </c>
     </row>
     <row r="94">
@@ -7011,13 +7011,13 @@
         <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D94" t="n">
-        <v>0.865934402443258</v>
+        <v>0.927701066998408</v>
       </c>
     </row>
     <row r="95">
@@ -7025,13 +7025,13 @@
         <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D95" t="n">
-        <v>0.863490160118197</v>
+        <v>0.926007329405816</v>
       </c>
     </row>
     <row r="96">
@@ -7039,13 +7039,13 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>0.863285013854652</v>
+        <v>0.925122141838942</v>
       </c>
     </row>
     <row r="97">
@@ -7053,13 +7053,13 @@
         <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>0.857419210424632</v>
+        <v>0.921402977513174</v>
       </c>
     </row>
     <row r="98">
@@ -7067,13 +7067,13 @@
         <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D98" t="n">
-        <v>0.852491876731506</v>
+        <v>0.876884692131801</v>
       </c>
     </row>
     <row r="99">
@@ -7081,13 +7081,13 @@
         <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D99" t="n">
-        <v>0.851807197646225</v>
+        <v>0.872552298826554</v>
       </c>
     </row>
     <row r="100">
@@ -7095,13 +7095,13 @@
         <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>0.847554825240091</v>
+        <v>0.862000465567786</v>
       </c>
     </row>
     <row r="101">
@@ -7109,13 +7109,13 @@
         <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>0.840734444477867</v>
+        <v>0.861572630514799</v>
       </c>
     </row>
     <row r="102">
@@ -7123,13 +7123,13 @@
         <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>0.839245973807264</v>
+        <v>0.861050557856968</v>
       </c>
     </row>
     <row r="103">
@@ -7137,13 +7137,13 @@
         <v>33</v>
       </c>
       <c r="B103" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D103" t="n">
-        <v>0.832702360953345</v>
+        <v>0.86031694584953</v>
       </c>
     </row>
     <row r="104">
@@ -7151,13 +7151,13 @@
         <v>33</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D104" t="n">
-        <v>0.755275481766351</v>
+        <v>0.859853886605218</v>
       </c>
     </row>
     <row r="105">
@@ -7165,13 +7165,13 @@
         <v>33</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>0.754589538340545</v>
+        <v>0.858374999659107</v>
       </c>
     </row>
     <row r="106">
@@ -7179,13 +7179,13 @@
         <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
-        <v>0.754355212897968</v>
+        <v>0.858260023434691</v>
       </c>
     </row>
     <row r="107">
@@ -7196,10 +7196,10 @@
         <v>21</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>0.748457359277169</v>
+        <v>0.856670779324573</v>
       </c>
     </row>
     <row r="108">
@@ -7207,13 +7207,13 @@
         <v>33</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D108" t="n">
-        <v>0.748428947730525</v>
+        <v>0.856392133694693</v>
       </c>
     </row>
     <row r="109">
@@ -7224,10 +7224,10 @@
         <v>20</v>
       </c>
       <c r="C109" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
-        <v>0.738730623015551</v>
+        <v>0.855363743907233</v>
       </c>
     </row>
     <row r="110">
@@ -7235,13 +7235,13 @@
         <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D110" t="n">
-        <v>0.73410622458265</v>
+        <v>0.85497360141275</v>
       </c>
     </row>
     <row r="111">
@@ -7249,13 +7249,13 @@
         <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D111" t="n">
-        <v>0.728760882684025</v>
+        <v>0.854047462886893</v>
       </c>
     </row>
     <row r="112">
@@ -7263,13 +7263,13 @@
         <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>0.725656553914708</v>
+        <v>0.853812978239326</v>
       </c>
     </row>
     <row r="113">
@@ -7277,13 +7277,13 @@
         <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D113" t="n">
-        <v>0.724107838519298</v>
+        <v>0.852970233080215</v>
       </c>
     </row>
     <row r="114">
@@ -7291,13 +7291,13 @@
         <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C114" t="s">
         <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>0.722389604050025</v>
+        <v>0.852242384010307</v>
       </c>
     </row>
     <row r="115">
@@ -7305,13 +7305,13 @@
         <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C115" t="s">
         <v>12</v>
       </c>
       <c r="D115" t="n">
-        <v>0.719205120390125</v>
+        <v>0.851903531359134</v>
       </c>
     </row>
     <row r="116">
@@ -7319,13 +7319,13 @@
         <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C116" t="s">
         <v>13</v>
       </c>
       <c r="D116" t="n">
-        <v>0.71826223950225</v>
+        <v>0.851122472431974</v>
       </c>
     </row>
     <row r="117">
@@ -7336,10 +7336,10 @@
         <v>18</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D117" t="n">
-        <v>0.717550458524028</v>
+        <v>0.850050517939039</v>
       </c>
     </row>
     <row r="118">
@@ -7347,13 +7347,13 @@
         <v>33</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
         <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>0.710591403324206</v>
+        <v>0.849822968337768</v>
       </c>
     </row>
     <row r="119">
@@ -7364,10 +7364,10 @@
         <v>20</v>
       </c>
       <c r="C119" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>0.70638321743828</v>
+        <v>0.847851111651972</v>
       </c>
     </row>
     <row r="120">
@@ -7375,13 +7375,13 @@
         <v>33</v>
       </c>
       <c r="B120" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D120" t="n">
-        <v>0.704766182540752</v>
+        <v>0.845766863420411</v>
       </c>
     </row>
     <row r="121">
@@ -7392,10 +7392,10 @@
         <v>18</v>
       </c>
       <c r="C121" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
-        <v>0.703956816878285</v>
+        <v>0.841562058073374</v>
       </c>
     </row>
     <row r="122">
@@ -7403,13 +7403,13 @@
         <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C122" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
-        <v>0.703899850143399</v>
+        <v>0.841485074844357</v>
       </c>
     </row>
     <row r="123">
@@ -7420,10 +7420,10 @@
         <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D123" t="n">
-        <v>0.703414835099036</v>
+        <v>0.841328250763489</v>
       </c>
     </row>
     <row r="124">
@@ -7431,13 +7431,13 @@
         <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C124" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D124" t="n">
-        <v>0.701639791568927</v>
+        <v>0.83581145462214</v>
       </c>
     </row>
     <row r="125">
@@ -7448,10 +7448,10 @@
         <v>20</v>
       </c>
       <c r="C125" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>0.701203110164173</v>
+        <v>0.835656013930563</v>
       </c>
     </row>
     <row r="126">
@@ -7459,13 +7459,13 @@
         <v>33</v>
       </c>
       <c r="B126" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C126" t="s">
         <v>10</v>
       </c>
       <c r="D126" t="n">
-        <v>0.700306100696184</v>
+        <v>0.832964382093162</v>
       </c>
     </row>
     <row r="127">
@@ -7473,13 +7473,13 @@
         <v>33</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>0.699776541810678</v>
+        <v>0.830070067992516</v>
       </c>
     </row>
     <row r="128">
@@ -7490,10 +7490,10 @@
         <v>21</v>
       </c>
       <c r="C128" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>0.693660419902171</v>
+        <v>0.829435496932033</v>
       </c>
     </row>
     <row r="129">
@@ -7501,13 +7501,13 @@
         <v>33</v>
       </c>
       <c r="B129" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>0.687179650560017</v>
+        <v>0.827347292199061</v>
       </c>
     </row>
     <row r="130">
@@ -7515,13 +7515,13 @@
         <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D130" t="n">
-        <v>0.677175198223825</v>
+        <v>0.824679541529282</v>
       </c>
     </row>
     <row r="131">
@@ -7529,13 +7529,13 @@
         <v>33</v>
       </c>
       <c r="B131" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D131" t="n">
-        <v>0.675986504426048</v>
+        <v>0.822058549962306</v>
       </c>
     </row>
     <row r="132">
@@ -7546,10 +7546,10 @@
         <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D132" t="n">
-        <v>0.665577257237551</v>
+        <v>0.821306226711607</v>
       </c>
     </row>
     <row r="133">
@@ -7560,10 +7560,10 @@
         <v>21</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D133" t="n">
-        <v>0.64408939800163</v>
+        <v>0.819479712277236</v>
       </c>
     </row>
     <row r="134">
@@ -7599,13 +7599,13 @@
         <v>34</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D136" t="n">
-        <v>0.998223029138366</v>
+        <v>0.996873764324862</v>
       </c>
     </row>
     <row r="137">
@@ -7613,13 +7613,13 @@
         <v>34</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D137" t="n">
-        <v>0.996873764324862</v>
+        <v>0.996431115508867</v>
       </c>
     </row>
     <row r="138">
@@ -7627,13 +7627,13 @@
         <v>34</v>
       </c>
       <c r="B138" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D138" t="n">
-        <v>0.996431115508867</v>
+        <v>0.99366212995493</v>
       </c>
     </row>
     <row r="139">
@@ -7641,13 +7641,13 @@
         <v>34</v>
       </c>
       <c r="B139" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>0.996162510114499</v>
+        <v>0.992943648564434</v>
       </c>
     </row>
     <row r="140">
@@ -7655,13 +7655,13 @@
         <v>34</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C140" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>0.99366212995493</v>
+        <v>0.981972656375355</v>
       </c>
     </row>
     <row r="141">
@@ -7669,13 +7669,13 @@
         <v>34</v>
       </c>
       <c r="B141" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D141" t="n">
-        <v>0.992943648564434</v>
+        <v>0.981901471594011</v>
       </c>
     </row>
     <row r="142">
@@ -7683,13 +7683,13 @@
         <v>34</v>
       </c>
       <c r="B142" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D142" t="n">
-        <v>0.992171891923539</v>
+        <v>0.981497941722016</v>
       </c>
     </row>
     <row r="143">
@@ -7697,13 +7697,13 @@
         <v>34</v>
       </c>
       <c r="B143" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C143" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D143" t="n">
-        <v>0.981972656375355</v>
+        <v>0.981216555076488</v>
       </c>
     </row>
     <row r="144">
@@ -7711,13 +7711,13 @@
         <v>34</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C144" t="s">
         <v>6</v>
       </c>
       <c r="D144" t="n">
-        <v>0.981901471594011</v>
+        <v>0.980884588188645</v>
       </c>
     </row>
     <row r="145">
@@ -7725,13 +7725,13 @@
         <v>34</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D145" t="n">
-        <v>0.981497941722016</v>
+        <v>0.980529726255368</v>
       </c>
     </row>
     <row r="146">
@@ -7739,13 +7739,13 @@
         <v>34</v>
       </c>
       <c r="B146" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C146" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D146" t="n">
-        <v>0.980884588188645</v>
+        <v>0.980081682413898</v>
       </c>
     </row>
     <row r="147">
@@ -7767,13 +7767,13 @@
         <v>34</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C148" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D148" t="n">
-        <v>0.979051586956825</v>
+        <v>0.9794794057144</v>
       </c>
     </row>
     <row r="149">
@@ -7781,13 +7781,13 @@
         <v>34</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C149" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D149" t="n">
-        <v>0.978253435016039</v>
+        <v>0.979477473373568</v>
       </c>
     </row>
     <row r="150">
@@ -7795,13 +7795,13 @@
         <v>34</v>
       </c>
       <c r="B150" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C150" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D150" t="n">
-        <v>0.976228967986917</v>
+        <v>0.979328028162334</v>
       </c>
     </row>
     <row r="151">
@@ -7809,13 +7809,13 @@
         <v>34</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C151" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D151" t="n">
-        <v>0.974573019518928</v>
+        <v>0.979112671719494</v>
       </c>
     </row>
     <row r="152">
@@ -7823,13 +7823,13 @@
         <v>34</v>
       </c>
       <c r="B152" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D152" t="n">
-        <v>0.940959481110758</v>
+        <v>0.979051586956825</v>
       </c>
     </row>
     <row r="153">
@@ -7837,13 +7837,13 @@
         <v>34</v>
       </c>
       <c r="B153" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" t="s">
         <v>16</v>
       </c>
-      <c r="C153" t="s">
-        <v>12</v>
-      </c>
       <c r="D153" t="n">
-        <v>0.939368354349732</v>
+        <v>0.978509584764313</v>
       </c>
     </row>
     <row r="154">
@@ -7851,13 +7851,13 @@
         <v>34</v>
       </c>
       <c r="B154" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D154" t="n">
-        <v>0.93922670863215</v>
+        <v>0.978253435016039</v>
       </c>
     </row>
     <row r="155">
@@ -7865,13 +7865,13 @@
         <v>34</v>
       </c>
       <c r="B155" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C155" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D155" t="n">
-        <v>0.938767769544249</v>
+        <v>0.978178186433008</v>
       </c>
     </row>
     <row r="156">
@@ -7879,13 +7879,13 @@
         <v>34</v>
       </c>
       <c r="B156" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C156" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D156" t="n">
-        <v>0.938518128140308</v>
+        <v>0.976228967986917</v>
       </c>
     </row>
     <row r="157">
@@ -7893,13 +7893,13 @@
         <v>34</v>
       </c>
       <c r="B157" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C157" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D157" t="n">
-        <v>0.937151258111362</v>
+        <v>0.975746620399439</v>
       </c>
     </row>
     <row r="158">
@@ -7907,13 +7907,13 @@
         <v>34</v>
       </c>
       <c r="B158" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C158" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D158" t="n">
-        <v>0.935333110732178</v>
+        <v>0.975246842922324</v>
       </c>
     </row>
     <row r="159">
@@ -7921,13 +7921,13 @@
         <v>34</v>
       </c>
       <c r="B159" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" t="s">
         <v>14</v>
       </c>
-      <c r="C159" t="s">
-        <v>13</v>
-      </c>
       <c r="D159" t="n">
-        <v>0.934671105540342</v>
+        <v>0.974773051234114</v>
       </c>
     </row>
     <row r="160">
@@ -7935,13 +7935,13 @@
         <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>0.932311727402187</v>
+        <v>0.974573019518928</v>
       </c>
     </row>
     <row r="161">
@@ -7949,13 +7949,13 @@
         <v>34</v>
       </c>
       <c r="B161" t="s">
+        <v>21</v>
+      </c>
+      <c r="C161" t="s">
         <v>14</v>
       </c>
-      <c r="C161" t="s">
-        <v>3</v>
-      </c>
       <c r="D161" t="n">
-        <v>0.930419732794081</v>
+        <v>0.971753467498275</v>
       </c>
     </row>
     <row r="162">
@@ -7963,13 +7963,13 @@
         <v>34</v>
       </c>
       <c r="B162" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C162" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D162" t="n">
-        <v>0.928987264615324</v>
+        <v>0.971672742488503</v>
       </c>
     </row>
     <row r="163">
@@ -7977,13 +7977,13 @@
         <v>34</v>
       </c>
       <c r="B163" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C163" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D163" t="n">
-        <v>0.928606527097934</v>
+        <v>0.970894404868297</v>
       </c>
     </row>
     <row r="164">
@@ -7994,10 +7994,10 @@
         <v>16</v>
       </c>
       <c r="C164" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D164" t="n">
-        <v>0.927582780939643</v>
+        <v>0.92647434991305</v>
       </c>
     </row>
     <row r="165">
@@ -8005,13 +8005,13 @@
         <v>34</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C165" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D165" t="n">
-        <v>0.926344129176296</v>
+        <v>0.925809980327506</v>
       </c>
     </row>
     <row r="166">
@@ -8019,13 +8019,13 @@
         <v>34</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D166" t="n">
-        <v>0.92440151675606</v>
+        <v>0.925027739203492</v>
       </c>
     </row>
     <row r="167">
@@ -8033,13 +8033,13 @@
         <v>34</v>
       </c>
       <c r="B167" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C167" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D167" t="n">
-        <v>0.92428311297854</v>
+        <v>0.924563592939192</v>
       </c>
     </row>
     <row r="168">
@@ -8047,13 +8047,13 @@
         <v>34</v>
       </c>
       <c r="B168" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C168" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D168" t="n">
-        <v>0.922157194924882</v>
+        <v>0.924277953390574</v>
       </c>
     </row>
     <row r="169">
@@ -8061,13 +8061,13 @@
         <v>34</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C169" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D169" t="n">
-        <v>0.920647630980508</v>
+        <v>0.92378619832135</v>
       </c>
     </row>
     <row r="170">
@@ -8075,13 +8075,13 @@
         <v>34</v>
       </c>
       <c r="B170" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C170" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D170" t="n">
-        <v>0.830804042574741</v>
+        <v>0.923646904474205</v>
       </c>
     </row>
     <row r="171">
@@ -8089,13 +8089,13 @@
         <v>34</v>
       </c>
       <c r="B171" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D171" t="n">
-        <v>0.830005095406198</v>
+        <v>0.922411767993241</v>
       </c>
     </row>
     <row r="172">
@@ -8106,10 +8106,10 @@
         <v>18</v>
       </c>
       <c r="C172" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D172" t="n">
-        <v>0.829974194233127</v>
+        <v>0.922229280129466</v>
       </c>
     </row>
     <row r="173">
@@ -8117,13 +8117,13 @@
         <v>34</v>
       </c>
       <c r="B173" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D173" t="n">
-        <v>0.828144465332218</v>
+        <v>0.921559903739872</v>
       </c>
     </row>
     <row r="174">
@@ -8131,13 +8131,13 @@
         <v>34</v>
       </c>
       <c r="B174" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D174" t="n">
-        <v>0.827254818367945</v>
+        <v>0.921377735219526</v>
       </c>
     </row>
     <row r="175">
@@ -8145,13 +8145,13 @@
         <v>34</v>
       </c>
       <c r="B175" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D175" t="n">
-        <v>0.826454717806073</v>
+        <v>0.920318111139967</v>
       </c>
     </row>
     <row r="176">
@@ -8159,13 +8159,13 @@
         <v>34</v>
       </c>
       <c r="B176" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C176" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D176" t="n">
-        <v>0.825259230003505</v>
+        <v>0.919299254066972</v>
       </c>
     </row>
     <row r="177">
@@ -8173,13 +8173,13 @@
         <v>34</v>
       </c>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C177" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D177" t="n">
-        <v>0.823437870405114</v>
+        <v>0.918928070553609</v>
       </c>
     </row>
     <row r="178">
@@ -8190,10 +8190,10 @@
         <v>18</v>
       </c>
       <c r="C178" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D178" t="n">
-        <v>0.817635265032349</v>
+        <v>0.916364452880955</v>
       </c>
     </row>
     <row r="179">
@@ -8201,13 +8201,13 @@
         <v>34</v>
       </c>
       <c r="B179" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C179" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D179" t="n">
-        <v>0.81681074033356</v>
+        <v>0.915962658734427</v>
       </c>
     </row>
     <row r="180">
@@ -8215,13 +8215,13 @@
         <v>34</v>
       </c>
       <c r="B180" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C180" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D180" t="n">
-        <v>0.81331669992378</v>
+        <v>0.915273106101698</v>
       </c>
     </row>
     <row r="181">
@@ -8229,13 +8229,13 @@
         <v>34</v>
       </c>
       <c r="B181" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D181" t="n">
-        <v>0.810926508275456</v>
+        <v>0.915264682949112</v>
       </c>
     </row>
     <row r="182">
@@ -8243,13 +8243,13 @@
         <v>34</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C182" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D182" t="n">
-        <v>0.810306591295356</v>
+        <v>0.914772627321365</v>
       </c>
     </row>
     <row r="183">
@@ -8257,13 +8257,13 @@
         <v>34</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>0.80971001644149</v>
+        <v>0.914170700021149</v>
       </c>
     </row>
     <row r="184">
@@ -8271,13 +8271,13 @@
         <v>34</v>
       </c>
       <c r="B184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D184" t="n">
-        <v>0.809077460975529</v>
+        <v>0.912984106246185</v>
       </c>
     </row>
     <row r="185">
@@ -8285,13 +8285,13 @@
         <v>34</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C185" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D185" t="n">
-        <v>0.808712154633603</v>
+        <v>0.912726844431379</v>
       </c>
     </row>
     <row r="186">
@@ -8299,13 +8299,13 @@
         <v>34</v>
       </c>
       <c r="B186" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C186" t="s">
         <v>6</v>
       </c>
       <c r="D186" t="n">
-        <v>0.808559938022328</v>
+        <v>0.912665532997491</v>
       </c>
     </row>
     <row r="187">
@@ -8313,13 +8313,13 @@
         <v>34</v>
       </c>
       <c r="B187" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C187" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D187" t="n">
-        <v>0.808495131343292</v>
+        <v>0.912352561408255</v>
       </c>
     </row>
     <row r="188">
@@ -8327,13 +8327,13 @@
         <v>34</v>
       </c>
       <c r="B188" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C188" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D188" t="n">
-        <v>0.807408445725784</v>
+        <v>0.911202619492754</v>
       </c>
     </row>
     <row r="189">
@@ -8341,13 +8341,13 @@
         <v>34</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C189" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D189" t="n">
-        <v>0.806116329610634</v>
+        <v>0.910912181026398</v>
       </c>
     </row>
     <row r="190">
@@ -8355,13 +8355,13 @@
         <v>34</v>
       </c>
       <c r="B190" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C190" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D190" t="n">
-        <v>0.805987381238292</v>
+        <v>0.910579902309088</v>
       </c>
     </row>
     <row r="191">
@@ -8372,10 +8372,10 @@
         <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>0.805380663786627</v>
+        <v>0.910235741511531</v>
       </c>
     </row>
     <row r="192">
@@ -8383,13 +8383,13 @@
         <v>34</v>
       </c>
       <c r="B192" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C192" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D192" t="n">
-        <v>0.804971106463934</v>
+        <v>0.910183995352614</v>
       </c>
     </row>
     <row r="193">
@@ -8397,13 +8397,13 @@
         <v>34</v>
       </c>
       <c r="B193" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C193" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>0.804917038490432</v>
+        <v>0.909369117330064</v>
       </c>
     </row>
     <row r="194">
@@ -8414,10 +8414,10 @@
         <v>20</v>
       </c>
       <c r="C194" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D194" t="n">
-        <v>0.804461718628069</v>
+        <v>0.906614835349502</v>
       </c>
     </row>
     <row r="195">
@@ -8425,13 +8425,13 @@
         <v>34</v>
       </c>
       <c r="B195" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
       </c>
       <c r="D195" t="n">
-        <v>0.803585545451884</v>
+        <v>0.905992159492632</v>
       </c>
     </row>
     <row r="196">
@@ -8439,13 +8439,13 @@
         <v>34</v>
       </c>
       <c r="B196" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C196" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D196" t="n">
-        <v>0.802241680673163</v>
+        <v>0.903939282169194</v>
       </c>
     </row>
     <row r="197">
@@ -8453,13 +8453,13 @@
         <v>34</v>
       </c>
       <c r="B197" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C197" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D197" t="n">
-        <v>0.798424389572686</v>
+        <v>0.903444015574567</v>
       </c>
     </row>
     <row r="198">
@@ -8467,13 +8467,13 @@
         <v>34</v>
       </c>
       <c r="B198" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C198" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D198" t="n">
-        <v>0.794141178912626</v>
+        <v>0.903242759083403</v>
       </c>
     </row>
     <row r="199">
@@ -8484,10 +8484,10 @@
         <v>21</v>
       </c>
       <c r="C199" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>0.793381566088358</v>
+        <v>0.9002729040074</v>
       </c>
     </row>
     <row r="200">
@@ -8509,13 +8509,13 @@
         <v>35</v>
       </c>
       <c r="B201" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C201" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D201" t="n">
-        <v>0.998009638849193</v>
+        <v>0.997608075793849</v>
       </c>
     </row>
     <row r="202">
@@ -8523,13 +8523,13 @@
         <v>35</v>
       </c>
       <c r="B202" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C202" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D202" t="n">
-        <v>0.997608075793849</v>
+        <v>0.968763947128625</v>
       </c>
     </row>
     <row r="203">
@@ -8537,13 +8537,13 @@
         <v>35</v>
       </c>
       <c r="B203" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C203" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D203" t="n">
-        <v>0.968208119244089</v>
+        <v>0.965565752733948</v>
       </c>
     </row>
     <row r="204">
@@ -8551,13 +8551,13 @@
         <v>35</v>
       </c>
       <c r="B204" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C204" t="s">
         <v>14</v>
       </c>
       <c r="D204" t="n">
-        <v>0.965025074251261</v>
+        <v>0.965469950957303</v>
       </c>
     </row>
     <row r="205">
@@ -8565,13 +8565,13 @@
         <v>35</v>
       </c>
       <c r="B205" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C205" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D205" t="n">
-        <v>0.962819882221282</v>
+        <v>0.963647450488854</v>
       </c>
     </row>
     <row r="206">
@@ -8579,13 +8579,13 @@
         <v>35</v>
       </c>
       <c r="B206" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C206" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D206" t="n">
-        <v>0.961627629233831</v>
+        <v>0.963014384073404</v>
       </c>
     </row>
     <row r="207">
@@ -8593,13 +8593,13 @@
         <v>35</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D207" t="n">
-        <v>0.955826451873771</v>
+        <v>0.962819882221282</v>
       </c>
     </row>
     <row r="208">
@@ -8607,13 +8607,13 @@
         <v>35</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>0.954873574910376</v>
+        <v>0.961627629233831</v>
       </c>
     </row>
     <row r="209">
@@ -8621,13 +8621,13 @@
         <v>35</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C209" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D209" t="n">
-        <v>0.952312456276701</v>
+        <v>0.961612844618915</v>
       </c>
     </row>
     <row r="210">
@@ -8635,13 +8635,13 @@
         <v>35</v>
       </c>
       <c r="B210" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C210" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
-        <v>0.950930942993345</v>
+        <v>0.961244302263566</v>
       </c>
     </row>
     <row r="211">
@@ -8649,13 +8649,13 @@
         <v>35</v>
       </c>
       <c r="B211" t="s">
+        <v>13</v>
+      </c>
+      <c r="C211" t="s">
         <v>10</v>
       </c>
-      <c r="C211" t="s">
-        <v>6</v>
-      </c>
       <c r="D211" t="n">
-        <v>0.950559763041546</v>
+        <v>0.955826451873771</v>
       </c>
     </row>
     <row r="212">
@@ -8663,13 +8663,13 @@
         <v>35</v>
       </c>
       <c r="B212" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212" t="s">
         <v>12</v>
       </c>
-      <c r="C212" t="s">
-        <v>6</v>
-      </c>
       <c r="D212" t="n">
-        <v>0.95039252975362</v>
+        <v>0.954873574910376</v>
       </c>
     </row>
     <row r="213">
@@ -8677,13 +8677,13 @@
         <v>35</v>
       </c>
       <c r="B213" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D213" t="n">
-        <v>0.946976813315906</v>
+        <v>0.952312456276701</v>
       </c>
     </row>
     <row r="214">
@@ -8691,13 +8691,13 @@
         <v>35</v>
       </c>
       <c r="B214" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C214" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D214" t="n">
-        <v>0.918754956358746</v>
+        <v>0.950930942993345</v>
       </c>
     </row>
     <row r="215">
@@ -8705,13 +8705,13 @@
         <v>35</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C215" t="s">
         <v>6</v>
       </c>
       <c r="D215" t="n">
-        <v>0.916982635151931</v>
+        <v>0.950559763041546</v>
       </c>
     </row>
     <row r="216">
@@ -8719,13 +8719,13 @@
         <v>35</v>
       </c>
       <c r="B216" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C216" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D216" t="n">
-        <v>0.916750745466097</v>
+        <v>0.95039252975362</v>
       </c>
     </row>
     <row r="217">
@@ -8733,13 +8733,13 @@
         <v>35</v>
       </c>
       <c r="B217" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C217" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D217" t="n">
-        <v>0.912505174190856</v>
+        <v>0.946976813315906</v>
       </c>
     </row>
     <row r="218">
@@ -8747,13 +8747,13 @@
         <v>35</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C218" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D218" t="n">
-        <v>0.909683460663694</v>
+        <v>0.93426862136154</v>
       </c>
     </row>
     <row r="219">
@@ -8761,13 +8761,13 @@
         <v>35</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C219" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D219" t="n">
-        <v>0.909190176269385</v>
+        <v>0.93280575794989</v>
       </c>
     </row>
     <row r="220">
@@ -8775,13 +8775,13 @@
         <v>35</v>
       </c>
       <c r="B220" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C220" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D220" t="n">
-        <v>0.905841318039986</v>
+        <v>0.931028125859507</v>
       </c>
     </row>
     <row r="221">
@@ -8789,13 +8789,13 @@
         <v>35</v>
       </c>
       <c r="B221" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C221" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D221" t="n">
-        <v>0.905561447712704</v>
+        <v>0.930447205095344</v>
       </c>
     </row>
     <row r="222">
@@ -8803,13 +8803,13 @@
         <v>35</v>
       </c>
       <c r="B222" t="s">
+        <v>21</v>
+      </c>
+      <c r="C222" t="s">
         <v>16</v>
       </c>
-      <c r="C222" t="s">
-        <v>6</v>
-      </c>
       <c r="D222" t="n">
-        <v>0.902961645129238</v>
+        <v>0.930185704153046</v>
       </c>
     </row>
     <row r="223">
@@ -8817,13 +8817,13 @@
         <v>35</v>
       </c>
       <c r="B223" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D223" t="n">
-        <v>0.898758780835165</v>
+        <v>0.928898807737566</v>
       </c>
     </row>
     <row r="224">
@@ -8831,13 +8831,13 @@
         <v>35</v>
       </c>
       <c r="B224" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D224" t="n">
-        <v>0.898643801677085</v>
+        <v>0.928468841238884</v>
       </c>
     </row>
     <row r="225">
@@ -8845,13 +8845,13 @@
         <v>35</v>
       </c>
       <c r="B225" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C225" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D225" t="n">
-        <v>0.898315120895752</v>
+        <v>0.92837769060537</v>
       </c>
     </row>
     <row r="226">
@@ -8859,13 +8859,13 @@
         <v>35</v>
       </c>
       <c r="B226" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C226" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D226" t="n">
-        <v>0.895806124725212</v>
+        <v>0.916982635151931</v>
       </c>
     </row>
     <row r="227">
@@ -8873,13 +8873,13 @@
         <v>35</v>
       </c>
       <c r="B227" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C227" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D227" t="n">
-        <v>0.895114615957435</v>
+        <v>0.916750745466097</v>
       </c>
     </row>
     <row r="228">
@@ -8887,13 +8887,13 @@
         <v>35</v>
       </c>
       <c r="B228" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C228" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D228" t="n">
-        <v>0.893998758630687</v>
+        <v>0.909683460663694</v>
       </c>
     </row>
     <row r="229">
@@ -8901,13 +8901,13 @@
         <v>35</v>
       </c>
       <c r="B229" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C229" t="s">
         <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>0.889986250476283</v>
+        <v>0.909190176269385</v>
       </c>
     </row>
     <row r="230">
@@ -8915,13 +8915,13 @@
         <v>35</v>
       </c>
       <c r="B230" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C230" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D230" t="n">
-        <v>0.888974698764439</v>
+        <v>0.905418350694502</v>
       </c>
     </row>
     <row r="231">
@@ -8929,13 +8929,13 @@
         <v>35</v>
       </c>
       <c r="B231" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C231" t="s">
         <v>8</v>
       </c>
       <c r="D231" t="n">
-        <v>0.885849844986442</v>
+        <v>0.90252242147675</v>
       </c>
     </row>
     <row r="232">
@@ -8943,13 +8943,13 @@
         <v>35</v>
       </c>
       <c r="B232" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C232" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D232" t="n">
-        <v>0.861676239763502</v>
+        <v>0.898361259133574</v>
       </c>
     </row>
     <row r="233">
@@ -8957,13 +8957,13 @@
         <v>35</v>
       </c>
       <c r="B233" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C233" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D233" t="n">
-        <v>0.859741839294369</v>
+        <v>0.897873073025394</v>
       </c>
     </row>
     <row r="234">
@@ -8971,13 +8971,13 @@
         <v>35</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C234" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D234" t="n">
-        <v>0.85053520988299</v>
+        <v>0.897243231866312</v>
       </c>
     </row>
     <row r="235">
@@ -8985,13 +8985,13 @@
         <v>35</v>
       </c>
       <c r="B235" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C235" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D235" t="n">
-        <v>0.848379941037306</v>
+        <v>0.895950220931004</v>
       </c>
     </row>
     <row r="236">
@@ -8999,13 +8999,13 @@
         <v>35</v>
       </c>
       <c r="B236" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C236" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>0.793535102652476</v>
+        <v>0.893602801024396</v>
       </c>
     </row>
     <row r="237">
@@ -9013,13 +9013,13 @@
         <v>35</v>
       </c>
       <c r="B237" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C237" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D237" t="n">
-        <v>0.793136440576215</v>
+        <v>0.893468761522935</v>
       </c>
     </row>
     <row r="238">
@@ -9030,10 +9030,10 @@
         <v>18</v>
       </c>
       <c r="C238" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D238" t="n">
-        <v>0.793078576799042</v>
+        <v>0.891289892683328</v>
       </c>
     </row>
     <row r="239">
@@ -9044,10 +9044,10 @@
         <v>20</v>
       </c>
       <c r="C239" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D239" t="n">
-        <v>0.785350284207826</v>
+        <v>0.890896949024968</v>
       </c>
     </row>
     <row r="240">
@@ -9055,13 +9055,13 @@
         <v>35</v>
       </c>
       <c r="B240" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C240" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D240" t="n">
-        <v>0.781680646238393</v>
+        <v>0.890699111717179</v>
       </c>
     </row>
     <row r="241">
@@ -9069,13 +9069,13 @@
         <v>35</v>
       </c>
       <c r="B241" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C241" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D241" t="n">
-        <v>0.781611534058525</v>
+        <v>0.887924976835861</v>
       </c>
     </row>
     <row r="242">
@@ -9083,13 +9083,13 @@
         <v>35</v>
       </c>
       <c r="B242" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C242" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D242" t="n">
-        <v>0.780024025351261</v>
+        <v>0.887361502241587</v>
       </c>
     </row>
     <row r="243">
@@ -9097,13 +9097,13 @@
         <v>35</v>
       </c>
       <c r="B243" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C243" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D243" t="n">
-        <v>0.777956947809422</v>
+        <v>0.887087584475339</v>
       </c>
     </row>
     <row r="244">
@@ -9114,10 +9114,10 @@
         <v>18</v>
       </c>
       <c r="C244" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D244" t="n">
-        <v>0.77304317973314</v>
+        <v>0.884535098328299</v>
       </c>
     </row>
     <row r="245">
@@ -9128,10 +9128,10 @@
         <v>20</v>
       </c>
       <c r="C245" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D245" t="n">
-        <v>0.770216039907194</v>
+        <v>0.883905818108557</v>
       </c>
     </row>
     <row r="246">
@@ -9139,13 +9139,13 @@
         <v>35</v>
       </c>
       <c r="B246" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C246" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D246" t="n">
-        <v>0.769663760731453</v>
+        <v>0.883812602387531</v>
       </c>
     </row>
     <row r="247">
@@ -9153,13 +9153,13 @@
         <v>35</v>
       </c>
       <c r="B247" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C247" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D247" t="n">
-        <v>0.769293567841974</v>
+        <v>0.883665968650807</v>
       </c>
     </row>
     <row r="248">
@@ -9167,13 +9167,13 @@
         <v>35</v>
       </c>
       <c r="B248" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C248" t="s">
         <v>10</v>
       </c>
       <c r="D248" t="n">
-        <v>0.760039444549066</v>
+        <v>0.882313818475489</v>
       </c>
     </row>
     <row r="249">
@@ -9181,13 +9181,13 @@
         <v>35</v>
       </c>
       <c r="B249" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C249" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D249" t="n">
-        <v>0.756463749902749</v>
+        <v>0.878774048043518</v>
       </c>
     </row>
     <row r="250">
@@ -9195,13 +9195,13 @@
         <v>35</v>
       </c>
       <c r="B250" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C250" t="s">
         <v>13</v>
       </c>
       <c r="D250" t="n">
-        <v>0.756163658498519</v>
+        <v>0.878648748995595</v>
       </c>
     </row>
     <row r="251">
@@ -9212,10 +9212,10 @@
         <v>20</v>
       </c>
       <c r="C251" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D251" t="n">
-        <v>0.752224423291595</v>
+        <v>0.877636498151588</v>
       </c>
     </row>
     <row r="252">
@@ -9226,10 +9226,10 @@
         <v>18</v>
       </c>
       <c r="C252" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D252" t="n">
-        <v>0.751726837387038</v>
+        <v>0.87721870532225</v>
       </c>
     </row>
     <row r="253">
@@ -9237,13 +9237,13 @@
         <v>35</v>
       </c>
       <c r="B253" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C253" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D253" t="n">
-        <v>0.751512929886741</v>
+        <v>0.876021321496337</v>
       </c>
     </row>
     <row r="254">
@@ -9251,13 +9251,13 @@
         <v>35</v>
       </c>
       <c r="B254" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C254" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D254" t="n">
-        <v>0.749540079838485</v>
+        <v>0.875954246313607</v>
       </c>
     </row>
     <row r="255">
@@ -9265,13 +9265,13 @@
         <v>35</v>
       </c>
       <c r="B255" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C255" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D255" t="n">
-        <v>0.748504408515421</v>
+        <v>0.875409906565435</v>
       </c>
     </row>
     <row r="256">
@@ -9279,13 +9279,13 @@
         <v>35</v>
       </c>
       <c r="B256" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C256" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D256" t="n">
-        <v>0.745845634708373</v>
+        <v>0.871799748073203</v>
       </c>
     </row>
     <row r="257">
@@ -9296,10 +9296,10 @@
         <v>18</v>
       </c>
       <c r="C257" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D257" t="n">
-        <v>0.742522698922669</v>
+        <v>0.870143101861005</v>
       </c>
     </row>
     <row r="258">
@@ -9307,13 +9307,13 @@
         <v>35</v>
       </c>
       <c r="B258" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C258" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D258" t="n">
-        <v>0.742414591430891</v>
+        <v>0.852210402427954</v>
       </c>
     </row>
     <row r="259">
@@ -9321,13 +9321,13 @@
         <v>35</v>
       </c>
       <c r="B259" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C259" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D259" t="n">
-        <v>0.732230050623761</v>
+        <v>0.849995344271259</v>
       </c>
     </row>
     <row r="260">
@@ -9335,13 +9335,13 @@
         <v>35</v>
       </c>
       <c r="B260" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C260" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>0.729008466514415</v>
+        <v>0.846636260534143</v>
       </c>
     </row>
     <row r="261">
@@ -9349,13 +9349,13 @@
         <v>35</v>
       </c>
       <c r="B261" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C261" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D261" t="n">
-        <v>0.728107980658433</v>
+        <v>0.844890392784049</v>
       </c>
     </row>
     <row r="262">
@@ -9363,13 +9363,13 @@
         <v>35</v>
       </c>
       <c r="B262" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C262" t="s">
         <v>10</v>
       </c>
       <c r="D262" t="n">
-        <v>0.71982394033162</v>
+        <v>0.837281319176401</v>
       </c>
     </row>
     <row r="263">
@@ -9377,13 +9377,13 @@
         <v>35</v>
       </c>
       <c r="B263" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C263" t="s">
         <v>12</v>
       </c>
       <c r="D263" t="n">
-        <v>0.718802088944346</v>
+        <v>0.834859059186078</v>
       </c>
     </row>
     <row r="264">
@@ -9394,10 +9394,10 @@
         <v>21</v>
       </c>
       <c r="C264" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D264" t="n">
-        <v>0.711863530150638</v>
+        <v>0.83177531747668</v>
       </c>
     </row>
     <row r="265">
@@ -9408,10 +9408,10 @@
         <v>21</v>
       </c>
       <c r="C265" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D265" t="n">
-        <v>0.69680898457086</v>
+        <v>0.829653902791547</v>
       </c>
     </row>
   </sheetData>
@@ -9453,27 +9453,27 @@
         <v>0.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="E2" t="n">
-        <v>0.815</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.76</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.78</v>
       </c>
     </row>
     <row r="4">
@@ -9484,13 +9484,13 @@
         <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="D4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.835</v>
       </c>
     </row>
     <row r="5">
@@ -9501,47 +9501,47 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="E5" t="n">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="D6" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>0.775</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="D7" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="E7" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -9552,13 +9552,13 @@
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="D8" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="E8" t="n">
-        <v>0.635</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="9">
@@ -9569,81 +9569,81 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="D9" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="E9" t="n">
-        <v>0.645</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="D10" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="E10" t="n">
-        <v>0.645</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="D11" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>0.615</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="D12" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="D13" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="E13" t="n">
-        <v>0.545</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="14">
@@ -9654,13 +9654,13 @@
         <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="D14" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="E14" t="n">
-        <v>0.745</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="15">
@@ -9671,30 +9671,30 @@
         <v>33</v>
       </c>
       <c r="C15" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.69</v>
+        <v>0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>0.74</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="D16" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -9705,13 +9705,13 @@
         <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="E17" t="n">
-        <v>0.72</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="18">
@@ -9722,30 +9722,30 @@
         <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="E18" t="n">
-        <v>0.71</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="E19" t="n">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="20">
@@ -9756,13 +9756,13 @@
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="D20" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.65</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="21">
@@ -9773,455 +9773,455 @@
         <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="E21" t="n">
-        <v>0.735</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="E22" t="n">
-        <v>0.725</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="D23" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="E23" t="n">
-        <v>0.665</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="E24" t="n">
-        <v>0.755</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="D25" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="E25" t="n">
-        <v>0.745</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="D26" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="E26" t="n">
-        <v>0.79</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="D27" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="E27" t="n">
-        <v>0.765</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="D28" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="E28" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="D29" t="n">
-        <v>0.66</v>
+        <v>0.86</v>
       </c>
       <c r="E29" t="n">
-        <v>0.755</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="D30" t="n">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
       <c r="E30" t="n">
-        <v>0.745</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="D31" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="E31" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="E32" t="n">
-        <v>0.71</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D33" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="E33" t="n">
-        <v>0.725</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="E34" t="n">
-        <v>0.72</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="D35" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="E35" t="n">
-        <v>0.785</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="D36" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="E36" t="n">
-        <v>0.78</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="D37" t="n">
-        <v>0.69</v>
+        <v>0.83</v>
       </c>
       <c r="E37" t="n">
-        <v>0.77</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
         <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="D38" t="n">
         <v>0.81</v>
       </c>
       <c r="E38" t="n">
-        <v>0.845</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="D39" t="n">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="E39" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="D40" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="E40" t="n">
-        <v>0.85</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="D41" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="E41" t="n">
-        <v>0.785</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="D42" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E42" t="n">
-        <v>0.765</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
         <v>35</v>
       </c>
       <c r="C43" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="D43" t="n">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="E43" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B44" t="s">
         <v>35</v>
       </c>
       <c r="C44" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="D44" t="n">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="E44" t="n">
-        <v>0.77</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
         <v>35</v>
       </c>
       <c r="C45" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="D45" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="E45" t="n">
-        <v>0.775</v>
+        <v>0.815</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
         <v>35</v>
       </c>
       <c r="C46" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="D46" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="E46" t="n">
-        <v>0.775</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
         <v>35</v>
       </c>
       <c r="C47" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="D47" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="E47" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="48">
@@ -10232,30 +10232,30 @@
         <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="E48" t="n">
-        <v>0.785</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
         <v>35</v>
       </c>
       <c r="C49" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="D49" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="n">
-        <v>0.775</v>
+        <v>0.815</v>
       </c>
     </row>
   </sheetData>

--- a/03_DEP/sensitivity_analysis/c_data/06_sensitivity_supplementary.xlsx
+++ b/03_DEP/sensitivity_analysis/c_data/06_sensitivity_supplementary.xlsx
@@ -37,10 +37,10 @@
     <t xml:space="preserve">None (limma handles NAs)</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr_none</t>
+    <t xml:space="preserve">quantile_none</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr</t>
+    <t xml:space="preserve">quantile</t>
   </si>
   <si>
     <t xml:space="preserve">vsn_none</t>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">bpca</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr_bpca</t>
+    <t xml:space="preserve">quantile_bpca</t>
   </si>
   <si>
     <t xml:space="preserve">vsn_bpca</t>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">mix_bpca_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr_mix_bpca_QRILC</t>
+    <t xml:space="preserve">quantile_mix_bpca_QRILC</t>
   </si>
   <si>
     <t xml:space="preserve">vsn_mix_bpca_QRILC</t>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">mix_RF_QRILC</t>
   </si>
   <si>
-    <t xml:space="preserve">rlr_mix_RF_QRILC</t>
+    <t xml:space="preserve">quantile_mix_RF_QRILC</t>
   </si>
   <si>
     <t xml:space="preserve">vsn_mix_RF_QRILC</t>
@@ -668,314 +668,314 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9169</v>
+        <v>0.9061</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9148</v>
+        <v>0.9026</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9428</v>
+        <v>0.9411</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9103</v>
+        <v>0.892</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8997</v>
+        <v>0.8887</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9168</v>
+        <v>0.904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9153</v>
+        <v>0.9027</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9462</v>
+        <v>0.9421</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9089</v>
+        <v>0.8775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8969</v>
+        <v>0.8936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9161</v>
+        <v>0.9019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.916</v>
+        <v>0.9035</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9446</v>
+        <v>0.942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9083</v>
+        <v>0.8712</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8954</v>
+        <v>0.8908</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9142</v>
+        <v>0.8948</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9115</v>
+        <v>0.8979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9496</v>
+        <v>0.9429</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8946</v>
+        <v>0.8462</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9011</v>
+        <v>0.8923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9141</v>
+        <v>0.8939</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9114</v>
+        <v>0.8973</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9429</v>
+        <v>0.9384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9092</v>
+        <v>0.8565</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8928</v>
+        <v>0.8833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9137</v>
+        <v>0.8881</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9138</v>
+        <v>0.8851</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9443</v>
+        <v>0.9411</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8982</v>
+        <v>0.8488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8986</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9129</v>
+        <v>0.8876</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9091</v>
+        <v>0.8842</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9428</v>
+        <v>0.9408</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9069</v>
+        <v>0.8485</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8929</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>0.912</v>
+        <v>0.887</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9121</v>
+        <v>0.8894</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9455</v>
+        <v>0.9391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8963</v>
+        <v>0.8424</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8943</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9057</v>
+        <v>0.8861</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9062</v>
+        <v>0.8857</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9509</v>
+        <v>0.9401</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8665</v>
+        <v>0.8427</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8993</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9041</v>
+        <v>0.8786</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9034</v>
+        <v>0.8861</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9516</v>
+        <v>0.9202</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8677</v>
+        <v>0.8428</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8939</v>
+        <v>0.8652</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9035</v>
+        <v>0.8761</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8974</v>
+        <v>0.879</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9442</v>
+        <v>0.9246</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8859</v>
+        <v>0.8375</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8866</v>
+        <v>0.8634</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9001</v>
+        <v>0.8602</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8936</v>
+        <v>0.8765</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9393</v>
+        <v>0.9285</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8844</v>
+        <v>0.7714</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8832</v>
+        <v>0.8646</v>
       </c>
     </row>
   </sheetData>
@@ -1014,13 +1014,13 @@
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D2" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E2" t="n">
-        <v>609</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3">
@@ -1031,13 +1031,13 @@
         <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>475</v>
+        <v>420</v>
       </c>
       <c r="D3" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="E3" t="n">
-        <v>669</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4">
@@ -1048,13 +1048,13 @@
         <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="D4" t="n">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="E4" t="n">
-        <v>667</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5">
@@ -1065,13 +1065,13 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D5" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E5" t="n">
-        <v>424</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6">
@@ -1082,13 +1082,13 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>323</v>
+        <v>1606</v>
       </c>
       <c r="D6" t="n">
-        <v>287</v>
+        <v>66</v>
       </c>
       <c r="E6" t="n">
-        <v>610</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="7">
@@ -1099,13 +1099,13 @@
         <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>511</v>
+        <v>1610</v>
       </c>
       <c r="D7" t="n">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
-        <v>692</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="8">
@@ -1116,13 +1116,13 @@
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>501</v>
+        <v>1608</v>
       </c>
       <c r="D8" t="n">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>677</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="9">
@@ -1133,13 +1133,13 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>234</v>
+        <v>1388</v>
       </c>
       <c r="D9" t="n">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>436</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="10">
@@ -1150,13 +1150,13 @@
         <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D10" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E10" t="n">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11">
@@ -1167,13 +1167,13 @@
         <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>540</v>
+        <v>473</v>
       </c>
       <c r="D11" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12">
@@ -1184,13 +1184,13 @@
         <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>554</v>
+        <v>491</v>
       </c>
       <c r="D12" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="E12" t="n">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13">
@@ -1201,13 +1201,13 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D13" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E13" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14">
@@ -1238,10 +1238,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1255,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1306,10 +1306,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1374,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1422,13 +1422,13 @@
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -1439,13 +1439,13 @@
         <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -1456,13 +1456,13 @@
         <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1473,13 +1473,13 @@
         <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1490,13 +1490,13 @@
         <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1510,10 +1510,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1524,13 +1524,13 @@
         <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1541,13 +1541,13 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1575,13 +1575,13 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1592,13 +1592,13 @@
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1626,13 +1626,13 @@
         <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="D38" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="E38" t="n">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39">
@@ -1643,13 +1643,13 @@
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D39" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="E39" t="n">
-        <v>121</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40">
@@ -1660,13 +1660,13 @@
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="D40" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E40" t="n">
-        <v>123</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41">
@@ -1677,13 +1677,13 @@
         <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D41" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="E41" t="n">
-        <v>93</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42">
@@ -1694,13 +1694,13 @@
         <v>35</v>
       </c>
       <c r="C42" t="n">
-        <v>91</v>
+        <v>370</v>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E42" t="n">
-        <v>158</v>
+        <v>409</v>
       </c>
     </row>
     <row r="43">
@@ -1711,13 +1711,13 @@
         <v>35</v>
       </c>
       <c r="C43" t="n">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E43" t="n">
-        <v>122</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44">
@@ -1728,13 +1728,13 @@
         <v>35</v>
       </c>
       <c r="C44" t="n">
-        <v>85</v>
+        <v>333</v>
       </c>
       <c r="D44" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>119</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45">
@@ -1745,13 +1745,13 @@
         <v>35</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>233</v>
       </c>
       <c r="D45" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E45" t="n">
-        <v>88</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46">
@@ -1762,13 +1762,13 @@
         <v>35</v>
       </c>
       <c r="C46" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D46" t="n">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="E46" t="n">
-        <v>194</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47">
@@ -1779,13 +1779,13 @@
         <v>35</v>
       </c>
       <c r="C47" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="D47" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E47" t="n">
-        <v>130</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48">
@@ -1796,13 +1796,13 @@
         <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="D48" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="E48" t="n">
-        <v>124</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49">
@@ -1813,13 +1813,13 @@
         <v>35</v>
       </c>
       <c r="C49" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="E49" t="n">
-        <v>101</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="E2" t="n">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="F2" t="n">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3">
@@ -1884,13 +1884,13 @@
         <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>604</v>
+        <v>534</v>
       </c>
       <c r="E3" t="n">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="F3" t="n">
-        <v>875</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1904,13 @@
         <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>591</v>
+        <v>538</v>
       </c>
       <c r="E4" t="n">
-        <v>272</v>
+        <v>321</v>
       </c>
       <c r="F4" t="n">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5">
@@ -1924,13 +1924,13 @@
         <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E5" t="n">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F5" t="n">
-        <v>697</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
@@ -1944,13 +1944,13 @@
         <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>437</v>
+        <v>1631</v>
       </c>
       <c r="E6" t="n">
-        <v>408</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>845</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="7">
@@ -1964,13 +1964,13 @@
         <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>1641</v>
       </c>
       <c r="E7" t="n">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>893</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="8">
@@ -1984,13 +1984,13 @@
         <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>627</v>
+        <v>1640</v>
       </c>
       <c r="E8" t="n">
-        <v>252</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>879</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="9">
@@ -2004,13 +2004,13 @@
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>373</v>
+        <v>1454</v>
       </c>
       <c r="E9" t="n">
-        <v>323</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>696</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="10">
@@ -2027,10 +2027,10 @@
         <v>492</v>
       </c>
       <c r="E10" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F10" t="n">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11">
@@ -2044,13 +2044,13 @@
         <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>664</v>
+        <v>584</v>
       </c>
       <c r="E11" t="n">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="F11" t="n">
-        <v>941</v>
+        <v>899</v>
       </c>
     </row>
     <row r="12">
@@ -2064,13 +2064,13 @@
         <v>37</v>
       </c>
       <c r="D12" t="n">
-        <v>671</v>
+        <v>612</v>
       </c>
       <c r="E12" t="n">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="F12" t="n">
-        <v>949</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13">
@@ -2084,13 +2084,13 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E13" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F13" t="n">
-        <v>722</v>
+        <v>714</v>
       </c>
     </row>
     <row r="14">
@@ -2104,13 +2104,13 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="E14" t="n">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="F14" t="n">
-        <v>772</v>
+        <v>757</v>
       </c>
     </row>
     <row r="15">
@@ -2124,13 +2124,13 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>578</v>
+        <v>503</v>
       </c>
       <c r="E15" t="n">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="F15" t="n">
-        <v>834</v>
+        <v>794</v>
       </c>
     </row>
     <row r="16">
@@ -2144,13 +2144,13 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="E16" t="n">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="F16" t="n">
-        <v>826</v>
+        <v>806</v>
       </c>
     </row>
     <row r="17">
@@ -2164,13 +2164,13 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E17" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F17" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18">
@@ -2184,13 +2184,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="n">
-        <v>408</v>
+        <v>1674</v>
       </c>
       <c r="E18" t="n">
-        <v>372</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>780</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="19">
@@ -2204,13 +2204,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>616</v>
+        <v>1692</v>
       </c>
       <c r="E19" t="n">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>855</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="20">
@@ -2224,13 +2224,13 @@
         <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>594</v>
+        <v>1688</v>
       </c>
       <c r="E20" t="n">
-        <v>231</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
-        <v>825</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="21">
@@ -2244,13 +2244,13 @@
         <v>38</v>
       </c>
       <c r="D21" t="n">
-        <v>315</v>
+        <v>1501</v>
       </c>
       <c r="E21" t="n">
-        <v>283</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
-        <v>598</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="22">
@@ -2264,13 +2264,13 @@
         <v>38</v>
       </c>
       <c r="D22" t="n">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="E22" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F22" t="n">
-        <v>823</v>
+        <v>810</v>
       </c>
     </row>
     <row r="23">
@@ -2284,13 +2284,13 @@
         <v>38</v>
       </c>
       <c r="D23" t="n">
-        <v>640</v>
+        <v>556</v>
       </c>
       <c r="E23" t="n">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="F23" t="n">
-        <v>906</v>
+        <v>850</v>
       </c>
     </row>
     <row r="24">
@@ -2304,13 +2304,13 @@
         <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>647</v>
+        <v>580</v>
       </c>
       <c r="E24" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="F24" t="n">
-        <v>914</v>
+        <v>865</v>
       </c>
     </row>
     <row r="25">
@@ -2327,10 +2327,10 @@
         <v>335</v>
       </c>
       <c r="E25" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F25" t="n">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="26">
@@ -2344,13 +2344,13 @@
         <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E26" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F26" t="n">
-        <v>609</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27">
@@ -2364,13 +2364,13 @@
         <v>39</v>
       </c>
       <c r="D27" t="n">
-        <v>475</v>
+        <v>420</v>
       </c>
       <c r="E27" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="F27" t="n">
-        <v>669</v>
+        <v>640</v>
       </c>
     </row>
     <row r="28">
@@ -2384,13 +2384,13 @@
         <v>39</v>
       </c>
       <c r="D28" t="n">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="E28" t="n">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="F28" t="n">
-        <v>667</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29">
@@ -2404,13 +2404,13 @@
         <v>39</v>
       </c>
       <c r="D29" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E29" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F29" t="n">
-        <v>424</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30">
@@ -2424,13 +2424,13 @@
         <v>39</v>
       </c>
       <c r="D30" t="n">
-        <v>323</v>
+        <v>1606</v>
       </c>
       <c r="E30" t="n">
-        <v>287</v>
+        <v>66</v>
       </c>
       <c r="F30" t="n">
-        <v>610</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="31">
@@ -2444,13 +2444,13 @@
         <v>39</v>
       </c>
       <c r="D31" t="n">
-        <v>511</v>
+        <v>1610</v>
       </c>
       <c r="E31" t="n">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="F31" t="n">
-        <v>692</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="32">
@@ -2464,13 +2464,13 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>501</v>
+        <v>1608</v>
       </c>
       <c r="E32" t="n">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="F32" t="n">
-        <v>677</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="33">
@@ -2484,13 +2484,13 @@
         <v>39</v>
       </c>
       <c r="D33" t="n">
-        <v>234</v>
+        <v>1388</v>
       </c>
       <c r="E33" t="n">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="F33" t="n">
-        <v>436</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="34">
@@ -2504,13 +2504,13 @@
         <v>39</v>
       </c>
       <c r="D34" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="E34" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F34" t="n">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="35">
@@ -2524,13 +2524,13 @@
         <v>39</v>
       </c>
       <c r="D35" t="n">
-        <v>540</v>
+        <v>473</v>
       </c>
       <c r="E35" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F35" t="n">
-        <v>760</v>
+        <v>707</v>
       </c>
     </row>
     <row r="36">
@@ -2544,13 +2544,13 @@
         <v>39</v>
       </c>
       <c r="D36" t="n">
-        <v>554</v>
+        <v>491</v>
       </c>
       <c r="E36" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F36" t="n">
-        <v>775</v>
+        <v>733</v>
       </c>
     </row>
     <row r="37">
@@ -2564,13 +2564,13 @@
         <v>39</v>
       </c>
       <c r="D37" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="E37" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F37" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38">
@@ -2584,13 +2584,13 @@
         <v>40</v>
       </c>
       <c r="D38" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E38" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F38" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39">
@@ -2604,13 +2604,13 @@
         <v>40</v>
       </c>
       <c r="D39" t="n">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="E39" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F39" t="n">
-        <v>417</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40">
@@ -2624,13 +2624,13 @@
         <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E40" t="n">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F40" t="n">
-        <v>414</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41">
@@ -2647,10 +2647,10 @@
         <v>107</v>
       </c>
       <c r="E41" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F41" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42">
@@ -2664,13 +2664,13 @@
         <v>40</v>
       </c>
       <c r="D42" t="n">
-        <v>157</v>
+        <v>1238</v>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="F42" t="n">
-        <v>342</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="43">
@@ -2684,13 +2684,13 @@
         <v>40</v>
       </c>
       <c r="D43" t="n">
-        <v>315</v>
+        <v>1281</v>
       </c>
       <c r="E43" t="n">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="F43" t="n">
-        <v>424</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="44">
@@ -2704,13 +2704,13 @@
         <v>40</v>
       </c>
       <c r="D44" t="n">
-        <v>314</v>
+        <v>1278</v>
       </c>
       <c r="E44" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
-        <v>420</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="45">
@@ -2724,13 +2724,13 @@
         <v>40</v>
       </c>
       <c r="D45" t="n">
-        <v>114</v>
+        <v>1029</v>
       </c>
       <c r="E45" t="n">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="F45" t="n">
-        <v>247</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="46">
@@ -2744,13 +2744,13 @@
         <v>40</v>
       </c>
       <c r="D46" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E46" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F46" t="n">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47">
@@ -2764,13 +2764,13 @@
         <v>40</v>
       </c>
       <c r="D47" t="n">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="E47" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F47" t="n">
-        <v>468</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48">
@@ -2784,13 +2784,13 @@
         <v>40</v>
       </c>
       <c r="D48" t="n">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="E48" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="F48" t="n">
-        <v>473</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49">
@@ -2804,13 +2804,13 @@
         <v>40</v>
       </c>
       <c r="D49" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E49" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F49" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50">
@@ -2824,13 +2824,13 @@
         <v>37</v>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E50" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F50" t="n">
-        <v>151</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51">
@@ -2844,13 +2844,13 @@
         <v>37</v>
       </c>
       <c r="D51" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E51" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F51" t="n">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52">
@@ -2864,13 +2864,13 @@
         <v>37</v>
       </c>
       <c r="D52" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E52" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F52" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53">
@@ -2884,13 +2884,13 @@
         <v>37</v>
       </c>
       <c r="D53" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="E53" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F53" t="n">
-        <v>145</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54">
@@ -2904,13 +2904,13 @@
         <v>37</v>
       </c>
       <c r="D54" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E54" t="n">
-        <v>57</v>
+        <v>359</v>
       </c>
       <c r="F54" t="n">
-        <v>149</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55">
@@ -2924,13 +2924,13 @@
         <v>37</v>
       </c>
       <c r="D55" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E55" t="n">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="F55" t="n">
-        <v>155</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56">
@@ -2944,13 +2944,13 @@
         <v>37</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E56" t="n">
-        <v>83</v>
+        <v>342</v>
       </c>
       <c r="F56" t="n">
-        <v>156</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57">
@@ -2964,13 +2964,13 @@
         <v>37</v>
       </c>
       <c r="D57" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E57" t="n">
-        <v>59</v>
+        <v>300</v>
       </c>
       <c r="F57" t="n">
-        <v>140</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58">
@@ -2984,13 +2984,13 @@
         <v>37</v>
       </c>
       <c r="D58" t="n">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="E58" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F58" t="n">
-        <v>164</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59">
@@ -3004,13 +3004,13 @@
         <v>37</v>
       </c>
       <c r="D59" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E59" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F59" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60">
@@ -3024,13 +3024,13 @@
         <v>37</v>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="E60" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="F60" t="n">
-        <v>166</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>37</v>
       </c>
       <c r="D61" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="E61" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="F61" t="n">
-        <v>162</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62">
@@ -3104,13 +3104,13 @@
         <v>38</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -3124,13 +3124,13 @@
         <v>38</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3144,13 +3144,13 @@
         <v>38</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -3167,10 +3167,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3187,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3247,10 +3247,10 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3264,13 +3264,13 @@
         <v>38</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -3327,10 +3327,10 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3347,10 +3347,10 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3487,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3507,10 +3507,10 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -3544,13 +3544,13 @@
         <v>40</v>
       </c>
       <c r="D86" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F86" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87">
@@ -3564,13 +3564,13 @@
         <v>40</v>
       </c>
       <c r="D87" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
@@ -3584,13 +3584,13 @@
         <v>40</v>
       </c>
       <c r="D88" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F88" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89">
@@ -3604,13 +3604,13 @@
         <v>40</v>
       </c>
       <c r="D89" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F89" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90">
@@ -3624,13 +3624,13 @@
         <v>40</v>
       </c>
       <c r="D90" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F90" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91">
@@ -3644,13 +3644,13 @@
         <v>40</v>
       </c>
       <c r="D91" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E91" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92">
@@ -3664,13 +3664,13 @@
         <v>40</v>
       </c>
       <c r="D92" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E92" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F92" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
@@ -3684,13 +3684,13 @@
         <v>40</v>
       </c>
       <c r="D93" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F93" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
     </row>
     <row r="94">
@@ -3704,13 +3704,13 @@
         <v>40</v>
       </c>
       <c r="D94" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
@@ -3724,13 +3724,13 @@
         <v>40</v>
       </c>
       <c r="D95" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F95" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
@@ -3744,13 +3744,13 @@
         <v>40</v>
       </c>
       <c r="D96" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E96" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F96" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="97">
@@ -3764,13 +3764,13 @@
         <v>40</v>
       </c>
       <c r="D97" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="98">
@@ -3784,13 +3784,13 @@
         <v>37</v>
       </c>
       <c r="D98" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="E98" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="F98" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="99">
@@ -3804,13 +3804,13 @@
         <v>37</v>
       </c>
       <c r="D99" t="n">
+        <v>117</v>
+      </c>
+      <c r="E99" t="n">
         <v>90</v>
       </c>
-      <c r="E99" t="n">
-        <v>71</v>
-      </c>
       <c r="F99" t="n">
-        <v>161</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100">
@@ -3824,13 +3824,13 @@
         <v>37</v>
       </c>
       <c r="D100" t="n">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="E100" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F100" t="n">
-        <v>175</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101">
@@ -3844,13 +3844,13 @@
         <v>37</v>
       </c>
       <c r="D101" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E101" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F101" t="n">
-        <v>176</v>
+        <v>230</v>
       </c>
     </row>
     <row r="102">
@@ -3864,13 +3864,13 @@
         <v>37</v>
       </c>
       <c r="D102" t="n">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="E102" t="n">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F102" t="n">
-        <v>176</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103">
@@ -3884,13 +3884,13 @@
         <v>37</v>
       </c>
       <c r="D103" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="E103" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F103" t="n">
-        <v>168</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104">
@@ -3904,13 +3904,13 @@
         <v>37</v>
       </c>
       <c r="D104" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="F104" t="n">
-        <v>161</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105">
@@ -3924,13 +3924,13 @@
         <v>37</v>
       </c>
       <c r="D105" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E105" t="n">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F105" t="n">
-        <v>176</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106">
@@ -3944,13 +3944,13 @@
         <v>37</v>
       </c>
       <c r="D106" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="E106" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F106" t="n">
-        <v>173</v>
+        <v>238</v>
       </c>
     </row>
     <row r="107">
@@ -3964,13 +3964,13 @@
         <v>37</v>
       </c>
       <c r="D107" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E107" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="F107" t="n">
-        <v>163</v>
+        <v>211</v>
       </c>
     </row>
     <row r="108">
@@ -3984,13 +3984,13 @@
         <v>37</v>
       </c>
       <c r="D108" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E108" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F108" t="n">
-        <v>167</v>
+        <v>222</v>
       </c>
     </row>
     <row r="109">
@@ -4004,13 +4004,13 @@
         <v>37</v>
       </c>
       <c r="D109" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="E109" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="F109" t="n">
-        <v>169</v>
+        <v>226</v>
       </c>
     </row>
     <row r="110">
@@ -4024,13 +4024,13 @@
         <v>38</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111">
@@ -4044,13 +4044,13 @@
         <v>38</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112">
@@ -4064,13 +4064,13 @@
         <v>38</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113">
@@ -4084,13 +4084,13 @@
         <v>38</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114">
@@ -4104,13 +4104,13 @@
         <v>38</v>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E114" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115">
@@ -4124,13 +4124,13 @@
         <v>38</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -4144,13 +4144,13 @@
         <v>38</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E116" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
@@ -4164,13 +4164,13 @@
         <v>38</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
@@ -4184,13 +4184,13 @@
         <v>38</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119">
@@ -4204,13 +4204,13 @@
         <v>38</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
@@ -4224,13 +4224,13 @@
         <v>38</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
@@ -4244,13 +4244,13 @@
         <v>38</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -4264,13 +4264,13 @@
         <v>39</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123">
@@ -4284,13 +4284,13 @@
         <v>39</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
@@ -4304,13 +4304,13 @@
         <v>39</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
         <v>2</v>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -4324,13 +4324,13 @@
         <v>39</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -4344,13 +4344,13 @@
         <v>39</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -4367,10 +4367,10 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -4384,13 +4384,13 @@
         <v>39</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F128" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
@@ -4404,13 +4404,13 @@
         <v>39</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
@@ -4444,13 +4444,13 @@
         <v>39</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -4464,13 +4464,13 @@
         <v>39</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -4487,10 +4487,10 @@
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -4504,13 +4504,13 @@
         <v>40</v>
       </c>
       <c r="D134" t="n">
+        <v>12</v>
+      </c>
+      <c r="E134" t="n">
         <v>10</v>
       </c>
-      <c r="E134" t="n">
-        <v>7</v>
-      </c>
       <c r="F134" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135">
@@ -4524,13 +4524,13 @@
         <v>40</v>
       </c>
       <c r="D135" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E135" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F135" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
@@ -4544,13 +4544,13 @@
         <v>40</v>
       </c>
       <c r="D136" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E136" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F136" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137">
@@ -4564,13 +4564,13 @@
         <v>40</v>
       </c>
       <c r="D137" t="n">
+        <v>14</v>
+      </c>
+      <c r="E137" t="n">
         <v>11</v>
       </c>
-      <c r="E137" t="n">
-        <v>8</v>
-      </c>
       <c r="F137" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138">
@@ -4584,13 +4584,13 @@
         <v>40</v>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E138" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F138" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139">
@@ -4604,13 +4604,13 @@
         <v>40</v>
       </c>
       <c r="D139" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E139" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F139" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140">
@@ -4624,13 +4624,13 @@
         <v>40</v>
       </c>
       <c r="D140" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E140" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F140" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141">
@@ -4644,13 +4644,13 @@
         <v>40</v>
       </c>
       <c r="D141" t="n">
+        <v>15</v>
+      </c>
+      <c r="E141" t="n">
         <v>11</v>
       </c>
-      <c r="E141" t="n">
-        <v>8</v>
-      </c>
       <c r="F141" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142">
@@ -4664,13 +4664,13 @@
         <v>40</v>
       </c>
       <c r="D142" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E142" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F142" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143">
@@ -4684,13 +4684,13 @@
         <v>40</v>
       </c>
       <c r="D143" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E143" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F143" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144">
@@ -4704,13 +4704,13 @@
         <v>40</v>
       </c>
       <c r="D144" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E144" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F144" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145">
@@ -4724,13 +4724,13 @@
         <v>40</v>
       </c>
       <c r="D145" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E145" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F145" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146">
@@ -4744,13 +4744,13 @@
         <v>37</v>
       </c>
       <c r="D146" t="n">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E146" t="n">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="F146" t="n">
-        <v>526</v>
+        <v>602</v>
       </c>
     </row>
     <row r="147">
@@ -4764,13 +4764,13 @@
         <v>37</v>
       </c>
       <c r="D147" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E147" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="F147" t="n">
-        <v>472</v>
+        <v>520</v>
       </c>
     </row>
     <row r="148">
@@ -4784,13 +4784,13 @@
         <v>37</v>
       </c>
       <c r="D148" t="n">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="E148" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="F148" t="n">
-        <v>457</v>
+        <v>530</v>
       </c>
     </row>
     <row r="149">
@@ -4804,13 +4804,13 @@
         <v>37</v>
       </c>
       <c r="D149" t="n">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="E149" t="n">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="F149" t="n">
-        <v>428</v>
+        <v>484</v>
       </c>
     </row>
     <row r="150">
@@ -4824,13 +4824,13 @@
         <v>37</v>
       </c>
       <c r="D150" t="n">
-        <v>260</v>
+        <v>663</v>
       </c>
       <c r="E150" t="n">
-        <v>262</v>
+        <v>94</v>
       </c>
       <c r="F150" t="n">
-        <v>522</v>
+        <v>757</v>
       </c>
     </row>
     <row r="151">
@@ -4844,13 +4844,13 @@
         <v>37</v>
       </c>
       <c r="D151" t="n">
-        <v>283</v>
+        <v>621</v>
       </c>
       <c r="E151" t="n">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="F151" t="n">
-        <v>458</v>
+        <v>697</v>
       </c>
     </row>
     <row r="152">
@@ -4864,13 +4864,13 @@
         <v>37</v>
       </c>
       <c r="D152" t="n">
-        <v>286</v>
+        <v>627</v>
       </c>
       <c r="E152" t="n">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="F152" t="n">
-        <v>456</v>
+        <v>710</v>
       </c>
     </row>
     <row r="153">
@@ -4884,13 +4884,13 @@
         <v>37</v>
       </c>
       <c r="D153" t="n">
-        <v>233</v>
+        <v>540</v>
       </c>
       <c r="E153" t="n">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="F153" t="n">
-        <v>431</v>
+        <v>622</v>
       </c>
     </row>
     <row r="154">
@@ -4904,13 +4904,13 @@
         <v>37</v>
       </c>
       <c r="D154" t="n">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="E154" t="n">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="F154" t="n">
-        <v>513</v>
+        <v>595</v>
       </c>
     </row>
     <row r="155">
@@ -4924,13 +4924,13 @@
         <v>37</v>
       </c>
       <c r="D155" t="n">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="E155" t="n">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="F155" t="n">
-        <v>461</v>
+        <v>539</v>
       </c>
     </row>
     <row r="156">
@@ -4944,13 +4944,13 @@
         <v>37</v>
       </c>
       <c r="D156" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="E156" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="F156" t="n">
-        <v>466</v>
+        <v>564</v>
       </c>
     </row>
     <row r="157">
@@ -4964,13 +4964,13 @@
         <v>37</v>
       </c>
       <c r="D157" t="n">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="E157" t="n">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="F157" t="n">
-        <v>443</v>
+        <v>503</v>
       </c>
     </row>
     <row r="158">
@@ -4984,13 +4984,13 @@
         <v>38</v>
       </c>
       <c r="D158" t="n">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="E158" t="n">
-        <v>150</v>
+        <v>227</v>
       </c>
       <c r="F158" t="n">
-        <v>296</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159">
@@ -5004,13 +5004,13 @@
         <v>38</v>
       </c>
       <c r="D159" t="n">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="E159" t="n">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="F159" t="n">
-        <v>236</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160">
@@ -5024,13 +5024,13 @@
         <v>38</v>
       </c>
       <c r="D160" t="n">
+        <v>175</v>
+      </c>
+      <c r="E160" t="n">
         <v>150</v>
       </c>
-      <c r="E160" t="n">
-        <v>92</v>
-      </c>
       <c r="F160" t="n">
-        <v>242</v>
+        <v>325</v>
       </c>
     </row>
     <row r="161">
@@ -5044,13 +5044,13 @@
         <v>38</v>
       </c>
       <c r="D161" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E161" t="n">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="F161" t="n">
-        <v>218</v>
+        <v>289</v>
       </c>
     </row>
     <row r="162">
@@ -5064,13 +5064,13 @@
         <v>38</v>
       </c>
       <c r="D162" t="n">
-        <v>155</v>
+        <v>548</v>
       </c>
       <c r="E162" t="n">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="F162" t="n">
-        <v>299</v>
+        <v>619</v>
       </c>
     </row>
     <row r="163">
@@ -5084,13 +5084,13 @@
         <v>38</v>
       </c>
       <c r="D163" t="n">
-        <v>144</v>
+        <v>490</v>
       </c>
       <c r="E163" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="F163" t="n">
-        <v>224</v>
+        <v>541</v>
       </c>
     </row>
     <row r="164">
@@ -5104,13 +5104,13 @@
         <v>38</v>
       </c>
       <c r="D164" t="n">
-        <v>141</v>
+        <v>500</v>
       </c>
       <c r="E164" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="F164" t="n">
-        <v>226</v>
+        <v>554</v>
       </c>
     </row>
     <row r="165">
@@ -5124,13 +5124,13 @@
         <v>38</v>
       </c>
       <c r="D165" t="n">
-        <v>110</v>
+        <v>384</v>
       </c>
       <c r="E165" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="F165" t="n">
-        <v>204</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166">
@@ -5144,13 +5144,13 @@
         <v>38</v>
       </c>
       <c r="D166" t="n">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="E166" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="F166" t="n">
-        <v>309</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167">
@@ -5164,13 +5164,13 @@
         <v>38</v>
       </c>
       <c r="D167" t="n">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="E167" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F167" t="n">
-        <v>249</v>
+        <v>336</v>
       </c>
     </row>
     <row r="168">
@@ -5184,13 +5184,13 @@
         <v>38</v>
       </c>
       <c r="D168" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="E168" t="n">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="F168" t="n">
-        <v>252</v>
+        <v>358</v>
       </c>
     </row>
     <row r="169">
@@ -5204,13 +5204,13 @@
         <v>38</v>
       </c>
       <c r="D169" t="n">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="E169" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="F169" t="n">
-        <v>236</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170">
@@ -5224,13 +5224,13 @@
         <v>39</v>
       </c>
       <c r="D170" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="E170" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="F170" t="n">
-        <v>166</v>
+        <v>252</v>
       </c>
     </row>
     <row r="171">
@@ -5244,13 +5244,13 @@
         <v>39</v>
       </c>
       <c r="D171" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E171" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F171" t="n">
-        <v>121</v>
+        <v>196</v>
       </c>
     </row>
     <row r="172">
@@ -5264,13 +5264,13 @@
         <v>39</v>
       </c>
       <c r="D172" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="E172" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="F172" t="n">
-        <v>123</v>
+        <v>202</v>
       </c>
     </row>
     <row r="173">
@@ -5284,13 +5284,13 @@
         <v>39</v>
       </c>
       <c r="D173" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E173" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="F173" t="n">
-        <v>93</v>
+        <v>156</v>
       </c>
     </row>
     <row r="174">
@@ -5304,13 +5304,13 @@
         <v>39</v>
       </c>
       <c r="D174" t="n">
-        <v>91</v>
+        <v>370</v>
       </c>
       <c r="E174" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="F174" t="n">
-        <v>158</v>
+        <v>409</v>
       </c>
     </row>
     <row r="175">
@@ -5324,13 +5324,13 @@
         <v>39</v>
       </c>
       <c r="D175" t="n">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="E175" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F175" t="n">
-        <v>122</v>
+        <v>333</v>
       </c>
     </row>
     <row r="176">
@@ -5344,13 +5344,13 @@
         <v>39</v>
       </c>
       <c r="D176" t="n">
-        <v>85</v>
+        <v>333</v>
       </c>
       <c r="E176" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F176" t="n">
-        <v>119</v>
+        <v>363</v>
       </c>
     </row>
     <row r="177">
@@ -5364,13 +5364,13 @@
         <v>39</v>
       </c>
       <c r="D177" t="n">
-        <v>61</v>
+        <v>233</v>
       </c>
       <c r="E177" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F177" t="n">
-        <v>88</v>
+        <v>257</v>
       </c>
     </row>
     <row r="178">
@@ -5384,13 +5384,13 @@
         <v>39</v>
       </c>
       <c r="D178" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="E178" t="n">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="F178" t="n">
-        <v>194</v>
+        <v>279</v>
       </c>
     </row>
     <row r="179">
@@ -5404,13 +5404,13 @@
         <v>39</v>
       </c>
       <c r="D179" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="E179" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="F179" t="n">
-        <v>130</v>
+        <v>228</v>
       </c>
     </row>
     <row r="180">
@@ -5424,13 +5424,13 @@
         <v>39</v>
       </c>
       <c r="D180" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="E180" t="n">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="F180" t="n">
-        <v>124</v>
+        <v>233</v>
       </c>
     </row>
     <row r="181">
@@ -5444,13 +5444,13 @@
         <v>39</v>
       </c>
       <c r="D181" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="E181" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="F181" t="n">
-        <v>101</v>
+        <v>183</v>
       </c>
     </row>
     <row r="182">
@@ -5464,13 +5464,13 @@
         <v>40</v>
       </c>
       <c r="D182" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E182" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F182" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="183">
@@ -5484,13 +5484,13 @@
         <v>40</v>
       </c>
       <c r="D183" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E183" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F183" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="184">
@@ -5507,10 +5507,10 @@
         <v>56</v>
       </c>
       <c r="E184" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F184" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
     </row>
     <row r="185">
@@ -5524,13 +5524,13 @@
         <v>40</v>
       </c>
       <c r="D185" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E185" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F185" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="186">
@@ -5544,13 +5544,13 @@
         <v>40</v>
       </c>
       <c r="D186" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E186" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F186" t="n">
-        <v>94</v>
+        <v>172</v>
       </c>
     </row>
     <row r="187">
@@ -5564,13 +5564,13 @@
         <v>40</v>
       </c>
       <c r="D187" t="n">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="E187" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F187" t="n">
-        <v>98</v>
+        <v>172</v>
       </c>
     </row>
     <row r="188">
@@ -5584,13 +5584,13 @@
         <v>40</v>
       </c>
       <c r="D188" t="n">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="E188" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F188" t="n">
-        <v>97</v>
+        <v>185</v>
       </c>
     </row>
     <row r="189">
@@ -5604,13 +5604,13 @@
         <v>40</v>
       </c>
       <c r="D189" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="E189" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F189" t="n">
-        <v>88</v>
+        <v>151</v>
       </c>
     </row>
     <row r="190">
@@ -5624,13 +5624,13 @@
         <v>40</v>
       </c>
       <c r="D190" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E190" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F190" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="191">
@@ -5644,13 +5644,13 @@
         <v>40</v>
       </c>
       <c r="D191" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E191" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F191" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="192">
@@ -5664,13 +5664,13 @@
         <v>40</v>
       </c>
       <c r="D192" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E192" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F192" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="193">
@@ -5684,13 +5684,13 @@
         <v>40</v>
       </c>
       <c r="D193" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E193" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F193" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5723,13 +5723,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>0.998355715707329</v>
+        <v>0.990494014295935</v>
       </c>
     </row>
     <row r="3">
@@ -5737,13 +5737,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>0.998322547706496</v>
+        <v>0.989459237472673</v>
       </c>
     </row>
     <row r="4">
@@ -5751,13 +5751,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0.992826254162618</v>
+        <v>0.987509003700604</v>
       </c>
     </row>
     <row r="5">
@@ -5765,13 +5765,13 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.99226723409611</v>
+        <v>0.96147718550514</v>
       </c>
     </row>
     <row r="6">
@@ -5779,13 +5779,13 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>0.99101150559939</v>
+        <v>0.957763665938366</v>
       </c>
     </row>
     <row r="7">
@@ -5793,13 +5793,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.990885649222845</v>
+        <v>0.956885607272462</v>
       </c>
     </row>
     <row r="8">
@@ -5807,13 +5807,13 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.990520538243959</v>
+        <v>0.955673278894309</v>
       </c>
     </row>
     <row r="9">
@@ -5821,13 +5821,13 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>0.990060537182612</v>
+        <v>0.954008991502472</v>
       </c>
     </row>
     <row r="10">
@@ -5835,13 +5835,13 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>0.989709392156393</v>
+        <v>0.953830817798301</v>
       </c>
     </row>
     <row r="11">
@@ -5849,13 +5849,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>0.960180273749328</v>
+        <v>0.950314440530974</v>
       </c>
     </row>
     <row r="12">
@@ -5863,13 +5863,13 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>0.959754925833271</v>
+        <v>0.946024831184802</v>
       </c>
     </row>
     <row r="13">
@@ -5877,13 +5877,13 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>0.959226506382697</v>
+        <v>0.928936434904087</v>
       </c>
     </row>
     <row r="14">
@@ -5891,13 +5891,13 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>0.958809190891762</v>
+        <v>0.927527000428408</v>
       </c>
     </row>
     <row r="15">
@@ -5905,13 +5905,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.958642940702152</v>
+        <v>0.915901316873489</v>
       </c>
     </row>
     <row r="16">
@@ -5919,13 +5919,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>0.956600571656048</v>
+        <v>0.911655762917275</v>
       </c>
     </row>
     <row r="17">
@@ -5933,13 +5933,13 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.95635237042836</v>
+        <v>0.909044721600146</v>
       </c>
     </row>
     <row r="18">
@@ -5950,10 +5950,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>0.955675463795456</v>
+        <v>0.907759747413299</v>
       </c>
     </row>
     <row r="19">
@@ -5961,13 +5961,13 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>0.955076540828136</v>
+        <v>0.906211089251383</v>
       </c>
     </row>
     <row r="20">
@@ -5975,13 +5975,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>12</v>
       </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
       <c r="D20" t="n">
-        <v>0.953762356597789</v>
+        <v>0.904788544403554</v>
       </c>
     </row>
     <row r="21">
@@ -5989,13 +5989,13 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.953621590243896</v>
+        <v>0.903850381279106</v>
       </c>
     </row>
     <row r="22">
@@ -6003,13 +6003,13 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.952876345787086</v>
+        <v>0.891698174660394</v>
       </c>
     </row>
     <row r="23">
@@ -6020,10 +6020,10 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>0.952451554353873</v>
+        <v>0.886335675673864</v>
       </c>
     </row>
     <row r="24">
@@ -6031,13 +6031,13 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>0.952089438771583</v>
+        <v>0.88587369268125</v>
       </c>
     </row>
     <row r="25">
@@ -6045,13 +6045,13 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.95023403495558</v>
+        <v>0.885411625520085</v>
       </c>
     </row>
     <row r="26">
@@ -6059,13 +6059,13 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.940731696573022</v>
+        <v>0.884367669995314</v>
       </c>
     </row>
     <row r="27">
@@ -6073,13 +6073,13 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
         <v>13</v>
       </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
       <c r="D27" t="n">
-        <v>0.940029977581778</v>
+        <v>0.881628947853451</v>
       </c>
     </row>
     <row r="28">
@@ -6087,13 +6087,13 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>0.908565216795165</v>
+        <v>0.878061551304229</v>
       </c>
     </row>
     <row r="29">
@@ -6101,13 +6101,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>0.905774411355432</v>
+        <v>0.875987542543257</v>
       </c>
     </row>
     <row r="30">
@@ -6115,13 +6115,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
       <c r="D30" t="n">
-        <v>0.90559529292107</v>
+        <v>0.856453712926877</v>
       </c>
     </row>
     <row r="31">
@@ -6129,13 +6129,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.905136238672441</v>
+        <v>0.852928813712436</v>
       </c>
     </row>
     <row r="32">
@@ -6143,13 +6143,13 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>0.894666995888018</v>
+        <v>0.851214782749031</v>
       </c>
     </row>
     <row r="33">
@@ -6157,13 +6157,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>0.893446469497374</v>
+        <v>0.847623943986188</v>
       </c>
     </row>
     <row r="34">
@@ -6171,13 +6171,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.881184051008863</v>
+        <v>0.847489742554272</v>
       </c>
     </row>
     <row r="35">
@@ -6185,13 +6185,13 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.880100333618833</v>
+        <v>0.846592236755845</v>
       </c>
     </row>
     <row r="36">
@@ -6199,13 +6199,13 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.879200727226391</v>
+        <v>0.837853835223252</v>
       </c>
     </row>
     <row r="37">
@@ -6213,13 +6213,13 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.877739134392136</v>
+        <v>0.836942572833833</v>
       </c>
     </row>
     <row r="38">
@@ -6227,13 +6227,13 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>0.877147133571808</v>
+        <v>0.836929143092506</v>
       </c>
     </row>
     <row r="39">
@@ -6244,10 +6244,10 @@
         <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>0.876124135982624</v>
+        <v>0.830237533502953</v>
       </c>
     </row>
     <row r="40">
@@ -6258,10 +6258,10 @@
         <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>0.874313452795428</v>
+        <v>0.82927641145375</v>
       </c>
     </row>
     <row r="41">
@@ -6269,13 +6269,13 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.872677064384096</v>
+        <v>0.827350635039457</v>
       </c>
     </row>
     <row r="42">
@@ -6283,13 +6283,13 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.872656862856641</v>
+        <v>0.822939610973918</v>
       </c>
     </row>
     <row r="43">
@@ -6297,13 +6297,13 @@
         <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.87226516225345</v>
+        <v>0.821571646450327</v>
       </c>
     </row>
     <row r="44">
@@ -6311,13 +6311,13 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>0.871063582960007</v>
+        <v>0.820032541461343</v>
       </c>
     </row>
     <row r="45">
@@ -6331,7 +6331,7 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.870561261648872</v>
+        <v>0.818525554655363</v>
       </c>
     </row>
     <row r="46">
@@ -6339,13 +6339,13 @@
         <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
         <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.870029515133027</v>
+        <v>0.810561759900822</v>
       </c>
     </row>
     <row r="47">
@@ -6353,13 +6353,13 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>0.869524876487136</v>
+        <v>0.810107681910582</v>
       </c>
     </row>
     <row r="48">
@@ -6367,13 +6367,13 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>0.859471338222732</v>
+        <v>0.809774471568299</v>
       </c>
     </row>
     <row r="49">
@@ -6381,13 +6381,13 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>0.857643979977167</v>
+        <v>0.80926583184826</v>
       </c>
     </row>
     <row r="50">
@@ -6395,13 +6395,13 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D50" t="n">
-        <v>0.856748050087452</v>
+        <v>0.805966478615209</v>
       </c>
     </row>
     <row r="51">
@@ -6409,13 +6409,13 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>0.856325404693441</v>
+        <v>0.794612244939256</v>
       </c>
     </row>
     <row r="52">
@@ -6423,13 +6423,13 @@
         <v>32</v>
       </c>
       <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" t="s">
         <v>16</v>
       </c>
-      <c r="C52" t="s">
-        <v>12</v>
-      </c>
       <c r="D52" t="n">
-        <v>0.81985340696391</v>
+        <v>0.79421740206002</v>
       </c>
     </row>
     <row r="53">
@@ -6437,13 +6437,13 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>0.818482633431156</v>
+        <v>0.790272861577593</v>
       </c>
     </row>
     <row r="54">
@@ -6451,13 +6451,13 @@
         <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D54" t="n">
-        <v>0.817618393680632</v>
+        <v>0.785300200230414</v>
       </c>
     </row>
     <row r="55">
@@ -6465,13 +6465,13 @@
         <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>0.81635097596205</v>
+        <v>0.784192446426461</v>
       </c>
     </row>
     <row r="56">
@@ -6479,13 +6479,13 @@
         <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>0.816172905056224</v>
+        <v>0.784142551256937</v>
       </c>
     </row>
     <row r="57">
@@ -6499,7 +6499,7 @@
         <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>0.815410654830923</v>
+        <v>0.781050678923977</v>
       </c>
     </row>
     <row r="58">
@@ -6507,13 +6507,13 @@
         <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>0.81490631763056</v>
+        <v>0.778915963794584</v>
       </c>
     </row>
     <row r="59">
@@ -6521,13 +6521,13 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>0.814293821941305</v>
+        <v>0.778450930009215</v>
       </c>
     </row>
     <row r="60">
@@ -6535,13 +6535,13 @@
         <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D60" t="n">
-        <v>0.812740054540192</v>
+        <v>0.770248701953712</v>
       </c>
     </row>
     <row r="61">
@@ -6549,13 +6549,13 @@
         <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D61" t="n">
-        <v>0.810989528196351</v>
+        <v>0.769023029293844</v>
       </c>
     </row>
     <row r="62">
@@ -6563,13 +6563,13 @@
         <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D62" t="n">
-        <v>0.808834290182036</v>
+        <v>0.758855112058402</v>
       </c>
     </row>
     <row r="63">
@@ -6577,13 +6577,13 @@
         <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>0.807040853191161</v>
+        <v>0.758240040361023</v>
       </c>
     </row>
     <row r="64">
@@ -6591,13 +6591,13 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>0.762800157229677</v>
+        <v>0.640178806692802</v>
       </c>
     </row>
     <row r="65">
@@ -6608,10 +6608,10 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>0.76130327810727</v>
+        <v>0.63769915719505</v>
       </c>
     </row>
     <row r="66">
@@ -6619,13 +6619,13 @@
         <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>0.760330108434314</v>
+        <v>0.626862547405447</v>
       </c>
     </row>
     <row r="67">
@@ -6633,13 +6633,13 @@
         <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>0.758868050269039</v>
+        <v>0.625935960619474</v>
       </c>
     </row>
     <row r="68">
@@ -6647,13 +6647,13 @@
         <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>0.998008760967842</v>
+        <v>0.976306602564918</v>
       </c>
     </row>
     <row r="69">
@@ -6661,13 +6661,13 @@
         <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>0.997673664558614</v>
+        <v>0.969980462894672</v>
       </c>
     </row>
     <row r="70">
@@ -6675,13 +6675,13 @@
         <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D70" t="n">
-        <v>0.975376717931088</v>
+        <v>0.954648784239546</v>
       </c>
     </row>
     <row r="71">
@@ -6689,13 +6689,13 @@
         <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D71" t="n">
-        <v>0.971935531215164</v>
+        <v>0.95392719092911</v>
       </c>
     </row>
     <row r="72">
@@ -6703,13 +6703,13 @@
         <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D72" t="n">
-        <v>0.968703363296826</v>
+        <v>0.95346548226049</v>
       </c>
     </row>
     <row r="73">
@@ -6717,13 +6717,13 @@
         <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>0.965178599544435</v>
+        <v>0.950871140702724</v>
       </c>
     </row>
     <row r="74">
@@ -6731,13 +6731,13 @@
         <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>0.963284345738104</v>
+        <v>0.950553328318896</v>
       </c>
     </row>
     <row r="75">
@@ -6745,13 +6745,13 @@
         <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0.959915346439877</v>
+        <v>0.949991161488937</v>
       </c>
     </row>
     <row r="76">
@@ -6759,13 +6759,13 @@
         <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D76" t="n">
-        <v>0.959273116746479</v>
+        <v>0.943997060061436</v>
       </c>
     </row>
     <row r="77">
@@ -6773,13 +6773,13 @@
         <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D77" t="n">
-        <v>0.958635392926261</v>
+        <v>0.937812582347252</v>
       </c>
     </row>
     <row r="78">
@@ -6787,13 +6787,13 @@
         <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D78" t="n">
-        <v>0.957899957530455</v>
+        <v>0.931867866670277</v>
       </c>
     </row>
     <row r="79">
@@ -6801,13 +6801,13 @@
         <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>0.957122084523631</v>
+        <v>0.931090968122224</v>
       </c>
     </row>
     <row r="80">
@@ -6815,13 +6815,13 @@
         <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>0.956952278977168</v>
+        <v>0.928968011227302</v>
       </c>
     </row>
     <row r="81">
@@ -6832,10 +6832,10 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D81" t="n">
-        <v>0.953016028192698</v>
+        <v>0.928765730433734</v>
       </c>
     </row>
     <row r="82">
@@ -6843,13 +6843,13 @@
         <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D82" t="n">
-        <v>0.952855888779202</v>
+        <v>0.928119018556011</v>
       </c>
     </row>
     <row r="83">
@@ -6857,13 +6857,13 @@
         <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>0.952507009312699</v>
+        <v>0.924188543559455</v>
       </c>
     </row>
     <row r="84">
@@ -6871,13 +6871,13 @@
         <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>0.95223357778627</v>
+        <v>0.921815408724356</v>
       </c>
     </row>
     <row r="85">
@@ -6885,13 +6885,13 @@
         <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>0.949338821647445</v>
+        <v>0.915612454525282</v>
       </c>
     </row>
     <row r="86">
@@ -6899,13 +6899,13 @@
         <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>0.941793623682258</v>
+        <v>0.899709406065513</v>
       </c>
     </row>
     <row r="87">
@@ -6913,13 +6913,13 @@
         <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>0.937102335950228</v>
+        <v>0.899699049245427</v>
       </c>
     </row>
     <row r="88">
@@ -6930,10 +6930,10 @@
         <v>20</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D88" t="n">
-        <v>0.936460637243553</v>
+        <v>0.898761147758568</v>
       </c>
     </row>
     <row r="89">
@@ -6941,13 +6941,13 @@
         <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>0.936145391428165</v>
+        <v>0.896098977712032</v>
       </c>
     </row>
     <row r="90">
@@ -6955,13 +6955,13 @@
         <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D90" t="n">
-        <v>0.935391340188886</v>
+        <v>0.894967610832027</v>
       </c>
     </row>
     <row r="91">
@@ -6969,13 +6969,13 @@
         <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>0.934093328117391</v>
+        <v>0.893320354261548</v>
       </c>
     </row>
     <row r="92">
@@ -6986,10 +6986,10 @@
         <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D92" t="n">
-        <v>0.933557099153161</v>
+        <v>0.89019498395591</v>
       </c>
     </row>
     <row r="93">
@@ -6997,13 +6997,13 @@
         <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>0.929959267448748</v>
+        <v>0.889399629529003</v>
       </c>
     </row>
     <row r="94">
@@ -7014,10 +7014,10 @@
         <v>21</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
-        <v>0.927701066998408</v>
+        <v>0.884962455645297</v>
       </c>
     </row>
     <row r="95">
@@ -7025,13 +7025,13 @@
         <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>0.926007329405816</v>
+        <v>0.882220957157003</v>
       </c>
     </row>
     <row r="96">
@@ -7039,13 +7039,13 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>0.925122141838942</v>
+        <v>0.877810599922465</v>
       </c>
     </row>
     <row r="97">
@@ -7053,13 +7053,13 @@
         <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>0.921402977513174</v>
+        <v>0.877272072804193</v>
       </c>
     </row>
     <row r="98">
@@ -7070,10 +7070,10 @@
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>0.876884692131801</v>
+        <v>0.876576450872866</v>
       </c>
     </row>
     <row r="99">
@@ -7081,13 +7081,13 @@
         <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>0.872552298826554</v>
+        <v>0.874459840002673</v>
       </c>
     </row>
     <row r="100">
@@ -7098,10 +7098,10 @@
         <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>0.862000465567786</v>
+        <v>0.874427584850768</v>
       </c>
     </row>
     <row r="101">
@@ -7109,13 +7109,13 @@
         <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>0.861572630514799</v>
+        <v>0.871848475480845</v>
       </c>
     </row>
     <row r="102">
@@ -7123,13 +7123,13 @@
         <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D102" t="n">
-        <v>0.861050557856968</v>
+        <v>0.869595424014114</v>
       </c>
     </row>
     <row r="103">
@@ -7137,13 +7137,13 @@
         <v>33</v>
       </c>
       <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="s">
         <v>14</v>
       </c>
-      <c r="C103" t="s">
-        <v>13</v>
-      </c>
       <c r="D103" t="n">
-        <v>0.86031694584953</v>
+        <v>0.867519123131056</v>
       </c>
     </row>
     <row r="104">
@@ -7151,13 +7151,13 @@
         <v>33</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C104" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D104" t="n">
-        <v>0.859853886605218</v>
+        <v>0.866701425596962</v>
       </c>
     </row>
     <row r="105">
@@ -7165,13 +7165,13 @@
         <v>33</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C105" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D105" t="n">
-        <v>0.858374999659107</v>
+        <v>0.863684713426959</v>
       </c>
     </row>
     <row r="106">
@@ -7179,13 +7179,13 @@
         <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D106" t="n">
-        <v>0.858260023434691</v>
+        <v>0.861871101678571</v>
       </c>
     </row>
     <row r="107">
@@ -7193,13 +7193,13 @@
         <v>33</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C107" t="s">
         <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>0.856670779324573</v>
+        <v>0.860725158770776</v>
       </c>
     </row>
     <row r="108">
@@ -7207,13 +7207,13 @@
         <v>33</v>
       </c>
       <c r="B108" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" t="s">
         <v>20</v>
       </c>
-      <c r="C108" t="s">
-        <v>13</v>
-      </c>
       <c r="D108" t="n">
-        <v>0.856392133694693</v>
+        <v>0.859607534591518</v>
       </c>
     </row>
     <row r="109">
@@ -7221,13 +7221,13 @@
         <v>33</v>
       </c>
       <c r="B109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>0.855363743907233</v>
+        <v>0.858603605165302</v>
       </c>
     </row>
     <row r="110">
@@ -7235,13 +7235,13 @@
         <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D110" t="n">
-        <v>0.85497360141275</v>
+        <v>0.858526549942008</v>
       </c>
     </row>
     <row r="111">
@@ -7249,13 +7249,13 @@
         <v>33</v>
       </c>
       <c r="B111" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" t="s">
         <v>16</v>
       </c>
-      <c r="C111" t="s">
-        <v>12</v>
-      </c>
       <c r="D111" t="n">
-        <v>0.854047462886893</v>
+        <v>0.85800225589648</v>
       </c>
     </row>
     <row r="112">
@@ -7263,13 +7263,13 @@
         <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D112" t="n">
-        <v>0.853812978239326</v>
+        <v>0.856800474225007</v>
       </c>
     </row>
     <row r="113">
@@ -7277,13 +7277,13 @@
         <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>0.852970233080215</v>
+        <v>0.854651325289345</v>
       </c>
     </row>
     <row r="114">
@@ -7294,10 +7294,10 @@
         <v>20</v>
       </c>
       <c r="C114" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D114" t="n">
-        <v>0.852242384010307</v>
+        <v>0.854430599177154</v>
       </c>
     </row>
     <row r="115">
@@ -7308,10 +7308,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D115" t="n">
-        <v>0.851903531359134</v>
+        <v>0.853413528318288</v>
       </c>
     </row>
     <row r="116">
@@ -7319,13 +7319,13 @@
         <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>0.851122472431974</v>
+        <v>0.851261434153436</v>
       </c>
     </row>
     <row r="117">
@@ -7333,13 +7333,13 @@
         <v>33</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
         <v>10</v>
       </c>
       <c r="D117" t="n">
-        <v>0.850050517939039</v>
+        <v>0.850848692060999</v>
       </c>
     </row>
     <row r="118">
@@ -7347,13 +7347,13 @@
         <v>33</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C118" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>0.849822968337768</v>
+        <v>0.846366674122005</v>
       </c>
     </row>
     <row r="119">
@@ -7364,10 +7364,10 @@
         <v>20</v>
       </c>
       <c r="C119" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D119" t="n">
-        <v>0.847851111651972</v>
+        <v>0.845528607178111</v>
       </c>
     </row>
     <row r="120">
@@ -7375,13 +7375,13 @@
         <v>33</v>
       </c>
       <c r="B120" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D120" t="n">
-        <v>0.845766863420411</v>
+        <v>0.831981171681126</v>
       </c>
     </row>
     <row r="121">
@@ -7389,13 +7389,13 @@
         <v>33</v>
       </c>
       <c r="B121" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C121" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>0.841562058073374</v>
+        <v>0.831702315088603</v>
       </c>
     </row>
     <row r="122">
@@ -7403,13 +7403,13 @@
         <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D122" t="n">
-        <v>0.841485074844357</v>
+        <v>0.831252168075425</v>
       </c>
     </row>
     <row r="123">
@@ -7417,13 +7417,13 @@
         <v>33</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
         <v>12</v>
       </c>
       <c r="D123" t="n">
-        <v>0.841328250763489</v>
+        <v>0.829572204409521</v>
       </c>
     </row>
     <row r="124">
@@ -7431,13 +7431,13 @@
         <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C124" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>0.83581145462214</v>
+        <v>0.828443292984989</v>
       </c>
     </row>
     <row r="125">
@@ -7448,10 +7448,10 @@
         <v>20</v>
       </c>
       <c r="C125" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D125" t="n">
-        <v>0.835656013930563</v>
+        <v>0.828018646751292</v>
       </c>
     </row>
     <row r="126">
@@ -7459,13 +7459,13 @@
         <v>33</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C126" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D126" t="n">
-        <v>0.832964382093162</v>
+        <v>0.826925572330916</v>
       </c>
     </row>
     <row r="127">
@@ -7473,13 +7473,13 @@
         <v>33</v>
       </c>
       <c r="B127" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C127" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D127" t="n">
-        <v>0.830070067992516</v>
+        <v>0.824964278984788</v>
       </c>
     </row>
     <row r="128">
@@ -7487,13 +7487,13 @@
         <v>33</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C128" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D128" t="n">
-        <v>0.829435496932033</v>
+        <v>0.820619939575436</v>
       </c>
     </row>
     <row r="129">
@@ -7501,13 +7501,13 @@
         <v>33</v>
       </c>
       <c r="B129" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C129" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D129" t="n">
-        <v>0.827347292199061</v>
+        <v>0.817951269631564</v>
       </c>
     </row>
     <row r="130">
@@ -7515,13 +7515,13 @@
         <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>0.824679541529282</v>
+        <v>0.798143613902192</v>
       </c>
     </row>
     <row r="131">
@@ -7529,13 +7529,13 @@
         <v>33</v>
       </c>
       <c r="B131" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C131" t="s">
         <v>6</v>
       </c>
       <c r="D131" t="n">
-        <v>0.822058549962306</v>
+        <v>0.794003320080744</v>
       </c>
     </row>
     <row r="132">
@@ -7546,10 +7546,10 @@
         <v>21</v>
       </c>
       <c r="C132" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D132" t="n">
-        <v>0.821306226711607</v>
+        <v>0.793211473408564</v>
       </c>
     </row>
     <row r="133">
@@ -7557,13 +7557,13 @@
         <v>33</v>
       </c>
       <c r="B133" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C133" t="s">
         <v>6</v>
       </c>
       <c r="D133" t="n">
-        <v>0.819479712277236</v>
+        <v>0.791739607264529</v>
       </c>
     </row>
     <row r="134">
@@ -7571,13 +7571,13 @@
         <v>34</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
         <v>10</v>
       </c>
       <c r="D134" t="n">
-        <v>0.998464346323567</v>
+        <v>0.992506553486782</v>
       </c>
     </row>
     <row r="135">
@@ -7585,13 +7585,13 @@
         <v>34</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C135" t="s">
         <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>0.99835285038275</v>
+        <v>0.991756047794236</v>
       </c>
     </row>
     <row r="136">
@@ -7602,10 +7602,10 @@
         <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D136" t="n">
-        <v>0.996873764324862</v>
+        <v>0.983118922521108</v>
       </c>
     </row>
     <row r="137">
@@ -7613,13 +7613,13 @@
         <v>34</v>
       </c>
       <c r="B137" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C137" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>0.996431115508867</v>
+        <v>0.982854211843706</v>
       </c>
     </row>
     <row r="138">
@@ -7627,13 +7627,13 @@
         <v>34</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C138" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D138" t="n">
-        <v>0.99366212995493</v>
+        <v>0.981893109690749</v>
       </c>
     </row>
     <row r="139">
@@ -7641,13 +7641,13 @@
         <v>34</v>
       </c>
       <c r="B139" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C139" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D139" t="n">
-        <v>0.992943648564434</v>
+        <v>0.979617135018887</v>
       </c>
     </row>
     <row r="140">
@@ -7655,13 +7655,13 @@
         <v>34</v>
       </c>
       <c r="B140" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C140" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D140" t="n">
-        <v>0.981972656375355</v>
+        <v>0.978063450888344</v>
       </c>
     </row>
     <row r="141">
@@ -7669,13 +7669,13 @@
         <v>34</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D141" t="n">
-        <v>0.981901471594011</v>
+        <v>0.976589671474346</v>
       </c>
     </row>
     <row r="142">
@@ -7683,13 +7683,13 @@
         <v>34</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C142" t="s">
         <v>8</v>
       </c>
       <c r="D142" t="n">
-        <v>0.981497941722016</v>
+        <v>0.97649538133233</v>
       </c>
     </row>
     <row r="143">
@@ -7697,13 +7697,13 @@
         <v>34</v>
       </c>
       <c r="B143" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>0.981216555076488</v>
+        <v>0.974518845430394</v>
       </c>
     </row>
     <row r="144">
@@ -7711,13 +7711,13 @@
         <v>34</v>
       </c>
       <c r="B144" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D144" t="n">
-        <v>0.980884588188645</v>
+        <v>0.972860335705076</v>
       </c>
     </row>
     <row r="145">
@@ -7728,10 +7728,10 @@
         <v>21</v>
       </c>
       <c r="C145" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D145" t="n">
-        <v>0.980529726255368</v>
+        <v>0.972491861689271</v>
       </c>
     </row>
     <row r="146">
@@ -7739,13 +7739,13 @@
         <v>34</v>
       </c>
       <c r="B146" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C146" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D146" t="n">
-        <v>0.980081682413898</v>
+        <v>0.969816565827293</v>
       </c>
     </row>
     <row r="147">
@@ -7753,13 +7753,13 @@
         <v>34</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C147" t="s">
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>0.979967397540461</v>
+        <v>0.967623229423342</v>
       </c>
     </row>
     <row r="148">
@@ -7767,13 +7767,13 @@
         <v>34</v>
       </c>
       <c r="B148" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9794794057144</v>
+        <v>0.9666854170876</v>
       </c>
     </row>
     <row r="149">
@@ -7781,13 +7781,13 @@
         <v>34</v>
       </c>
       <c r="B149" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D149" t="n">
-        <v>0.979477473373568</v>
+        <v>0.966406868613501</v>
       </c>
     </row>
     <row r="150">
@@ -7795,13 +7795,13 @@
         <v>34</v>
       </c>
       <c r="B150" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D150" t="n">
-        <v>0.979328028162334</v>
+        <v>0.966373556008576</v>
       </c>
     </row>
     <row r="151">
@@ -7809,13 +7809,13 @@
         <v>34</v>
       </c>
       <c r="B151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C151" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D151" t="n">
-        <v>0.979112671719494</v>
+        <v>0.965698298224587</v>
       </c>
     </row>
     <row r="152">
@@ -7829,7 +7829,7 @@
         <v>8</v>
       </c>
       <c r="D152" t="n">
-        <v>0.979051586956825</v>
+        <v>0.958511797653702</v>
       </c>
     </row>
     <row r="153">
@@ -7837,13 +7837,13 @@
         <v>34</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>0.978509584764313</v>
+        <v>0.958395242817624</v>
       </c>
     </row>
     <row r="154">
@@ -7851,13 +7851,13 @@
         <v>34</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D154" t="n">
-        <v>0.978253435016039</v>
+        <v>0.954215379583543</v>
       </c>
     </row>
     <row r="155">
@@ -7865,13 +7865,13 @@
         <v>34</v>
       </c>
       <c r="B155" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C155" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D155" t="n">
-        <v>0.978178186433008</v>
+        <v>0.948726149646208</v>
       </c>
     </row>
     <row r="156">
@@ -7879,13 +7879,13 @@
         <v>34</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C156" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D156" t="n">
-        <v>0.976228967986917</v>
+        <v>0.948624289090454</v>
       </c>
     </row>
     <row r="157">
@@ -7893,13 +7893,13 @@
         <v>34</v>
       </c>
       <c r="B157" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D157" t="n">
-        <v>0.975746620399439</v>
+        <v>0.946301052857023</v>
       </c>
     </row>
     <row r="158">
@@ -7907,13 +7907,13 @@
         <v>34</v>
       </c>
       <c r="B158" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C158" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D158" t="n">
-        <v>0.975246842922324</v>
+        <v>0.945913653425988</v>
       </c>
     </row>
     <row r="159">
@@ -7921,13 +7921,13 @@
         <v>34</v>
       </c>
       <c r="B159" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
       </c>
       <c r="D159" t="n">
-        <v>0.974773051234114</v>
+        <v>0.945379167922183</v>
       </c>
     </row>
     <row r="160">
@@ -7935,13 +7935,13 @@
         <v>34</v>
       </c>
       <c r="B160" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C160" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D160" t="n">
-        <v>0.974573019518928</v>
+        <v>0.945355877370306</v>
       </c>
     </row>
     <row r="161">
@@ -7949,13 +7949,13 @@
         <v>34</v>
       </c>
       <c r="B161" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C161" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D161" t="n">
-        <v>0.971753467498275</v>
+        <v>0.943953433407905</v>
       </c>
     </row>
     <row r="162">
@@ -7963,13 +7963,13 @@
         <v>34</v>
       </c>
       <c r="B162" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C162" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D162" t="n">
-        <v>0.971672742488503</v>
+        <v>0.942230568458994</v>
       </c>
     </row>
     <row r="163">
@@ -7977,13 +7977,13 @@
         <v>34</v>
       </c>
       <c r="B163" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D163" t="n">
-        <v>0.970894404868297</v>
+        <v>0.942011215951743</v>
       </c>
     </row>
     <row r="164">
@@ -7991,13 +7991,13 @@
         <v>34</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D164" t="n">
-        <v>0.92647434991305</v>
+        <v>0.939599218656257</v>
       </c>
     </row>
     <row r="165">
@@ -8005,13 +8005,13 @@
         <v>34</v>
       </c>
       <c r="B165" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C165" t="s">
         <v>10</v>
       </c>
       <c r="D165" t="n">
-        <v>0.925809980327506</v>
+        <v>0.938974718018143</v>
       </c>
     </row>
     <row r="166">
@@ -8019,13 +8019,13 @@
         <v>34</v>
       </c>
       <c r="B166" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C166" t="s">
         <v>13</v>
       </c>
       <c r="D166" t="n">
-        <v>0.925027739203492</v>
+        <v>0.935458657545544</v>
       </c>
     </row>
     <row r="167">
@@ -8033,13 +8033,13 @@
         <v>34</v>
       </c>
       <c r="B167" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>0.924563592939192</v>
+        <v>0.934044387347426</v>
       </c>
     </row>
     <row r="168">
@@ -8047,13 +8047,13 @@
         <v>34</v>
       </c>
       <c r="B168" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C168" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D168" t="n">
-        <v>0.924277953390574</v>
+        <v>0.93387368318232</v>
       </c>
     </row>
     <row r="169">
@@ -8061,13 +8061,13 @@
         <v>34</v>
       </c>
       <c r="B169" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C169" t="s">
         <v>10</v>
       </c>
       <c r="D169" t="n">
-        <v>0.92378619832135</v>
+        <v>0.932191605095795</v>
       </c>
     </row>
     <row r="170">
@@ -8075,13 +8075,13 @@
         <v>34</v>
       </c>
       <c r="B170" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C170" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D170" t="n">
-        <v>0.923646904474205</v>
+        <v>0.931595818499899</v>
       </c>
     </row>
     <row r="171">
@@ -8089,13 +8089,13 @@
         <v>34</v>
       </c>
       <c r="B171" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C171" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>0.922411767993241</v>
+        <v>0.931230137077488</v>
       </c>
     </row>
     <row r="172">
@@ -8103,13 +8103,13 @@
         <v>34</v>
       </c>
       <c r="B172" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D172" t="n">
-        <v>0.922229280129466</v>
+        <v>0.931000739335657</v>
       </c>
     </row>
     <row r="173">
@@ -8120,10 +8120,10 @@
         <v>17</v>
       </c>
       <c r="C173" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D173" t="n">
-        <v>0.921559903739872</v>
+        <v>0.929065380915787</v>
       </c>
     </row>
     <row r="174">
@@ -8131,13 +8131,13 @@
         <v>34</v>
       </c>
       <c r="B174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C174" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D174" t="n">
-        <v>0.921377735219526</v>
+        <v>0.928157860290909</v>
       </c>
     </row>
     <row r="175">
@@ -8145,13 +8145,13 @@
         <v>34</v>
       </c>
       <c r="B175" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C175" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D175" t="n">
-        <v>0.920318111139967</v>
+        <v>0.92560065887262</v>
       </c>
     </row>
     <row r="176">
@@ -8162,10 +8162,10 @@
         <v>21</v>
       </c>
       <c r="C176" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>0.919299254066972</v>
+        <v>0.92458753076862</v>
       </c>
     </row>
     <row r="177">
@@ -8173,13 +8173,13 @@
         <v>34</v>
       </c>
       <c r="B177" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D177" t="n">
-        <v>0.918928070553609</v>
+        <v>0.924580332625246</v>
       </c>
     </row>
     <row r="178">
@@ -8187,13 +8187,13 @@
         <v>34</v>
       </c>
       <c r="B178" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D178" t="n">
-        <v>0.916364452880955</v>
+        <v>0.92413236197202</v>
       </c>
     </row>
     <row r="179">
@@ -8201,13 +8201,13 @@
         <v>34</v>
       </c>
       <c r="B179" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C179" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>0.915962658734427</v>
+        <v>0.922399477165426</v>
       </c>
     </row>
     <row r="180">
@@ -8215,13 +8215,13 @@
         <v>34</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C180" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D180" t="n">
-        <v>0.915273106101698</v>
+        <v>0.921498875567375</v>
       </c>
     </row>
     <row r="181">
@@ -8232,10 +8232,10 @@
         <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D181" t="n">
-        <v>0.915264682949112</v>
+        <v>0.918898595057072</v>
       </c>
     </row>
     <row r="182">
@@ -8246,10 +8246,10 @@
         <v>17</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D182" t="n">
-        <v>0.914772627321365</v>
+        <v>0.916046468798796</v>
       </c>
     </row>
     <row r="183">
@@ -8257,13 +8257,13 @@
         <v>34</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C183" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D183" t="n">
-        <v>0.914170700021149</v>
+        <v>0.915520802740097</v>
       </c>
     </row>
     <row r="184">
@@ -8274,10 +8274,10 @@
         <v>21</v>
       </c>
       <c r="C184" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D184" t="n">
-        <v>0.912984106246185</v>
+        <v>0.912184876142492</v>
       </c>
     </row>
     <row r="185">
@@ -8285,13 +8285,13 @@
         <v>34</v>
       </c>
       <c r="B185" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C185" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D185" t="n">
-        <v>0.912726844431379</v>
+        <v>0.911956842877506</v>
       </c>
     </row>
     <row r="186">
@@ -8299,13 +8299,13 @@
         <v>34</v>
       </c>
       <c r="B186" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C186" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D186" t="n">
-        <v>0.912665532997491</v>
+        <v>0.90777762298699</v>
       </c>
     </row>
     <row r="187">
@@ -8313,13 +8313,13 @@
         <v>34</v>
       </c>
       <c r="B187" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D187" t="n">
-        <v>0.912352561408255</v>
+        <v>0.9072054457882</v>
       </c>
     </row>
     <row r="188">
@@ -8327,13 +8327,13 @@
         <v>34</v>
       </c>
       <c r="B188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C188" t="s">
         <v>6</v>
       </c>
       <c r="D188" t="n">
-        <v>0.911202619492754</v>
+        <v>0.899052929922983</v>
       </c>
     </row>
     <row r="189">
@@ -8341,13 +8341,13 @@
         <v>34</v>
       </c>
       <c r="B189" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C189" t="s">
         <v>6</v>
       </c>
       <c r="D189" t="n">
-        <v>0.910912181026398</v>
+        <v>0.897774960678635</v>
       </c>
     </row>
     <row r="190">
@@ -8355,13 +8355,13 @@
         <v>34</v>
       </c>
       <c r="B190" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C190" t="s">
         <v>6</v>
       </c>
       <c r="D190" t="n">
-        <v>0.910579902309088</v>
+        <v>0.895995998688093</v>
       </c>
     </row>
     <row r="191">
@@ -8369,13 +8369,13 @@
         <v>34</v>
       </c>
       <c r="B191" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D191" t="n">
-        <v>0.910235741511531</v>
+        <v>0.895860347991647</v>
       </c>
     </row>
     <row r="192">
@@ -8383,13 +8383,13 @@
         <v>34</v>
       </c>
       <c r="B192" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>0.910183995352614</v>
+        <v>0.891929486653056</v>
       </c>
     </row>
     <row r="193">
@@ -8397,13 +8397,13 @@
         <v>34</v>
       </c>
       <c r="B193" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C193" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D193" t="n">
-        <v>0.909369117330064</v>
+        <v>0.891034033209035</v>
       </c>
     </row>
     <row r="194">
@@ -8414,10 +8414,10 @@
         <v>20</v>
       </c>
       <c r="C194" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D194" t="n">
-        <v>0.906614835349502</v>
+        <v>0.889557096898744</v>
       </c>
     </row>
     <row r="195">
@@ -8425,13 +8425,13 @@
         <v>34</v>
       </c>
       <c r="B195" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C195" t="s">
         <v>8</v>
       </c>
       <c r="D195" t="n">
-        <v>0.905992159492632</v>
+        <v>0.889051870834351</v>
       </c>
     </row>
     <row r="196">
@@ -8439,13 +8439,13 @@
         <v>34</v>
       </c>
       <c r="B196" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C196" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D196" t="n">
-        <v>0.903939282169194</v>
+        <v>0.885209208373757</v>
       </c>
     </row>
     <row r="197">
@@ -8453,13 +8453,13 @@
         <v>34</v>
       </c>
       <c r="B197" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C197" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D197" t="n">
-        <v>0.903444015574567</v>
+        <v>0.883803606131967</v>
       </c>
     </row>
     <row r="198">
@@ -8467,13 +8467,13 @@
         <v>34</v>
       </c>
       <c r="B198" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C198" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D198" t="n">
-        <v>0.903242759083403</v>
+        <v>0.882708599821823</v>
       </c>
     </row>
     <row r="199">
@@ -8481,13 +8481,13 @@
         <v>34</v>
       </c>
       <c r="B199" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C199" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D199" t="n">
-        <v>0.9002729040074</v>
+        <v>0.880030632268437</v>
       </c>
     </row>
     <row r="200">
@@ -8495,13 +8495,13 @@
         <v>35</v>
       </c>
       <c r="B200" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D200" t="n">
-        <v>0.998131505311355</v>
+        <v>0.965592530533865</v>
       </c>
     </row>
     <row r="201">
@@ -8509,13 +8509,13 @@
         <v>35</v>
       </c>
       <c r="B201" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C201" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D201" t="n">
-        <v>0.997608075793849</v>
+        <v>0.961215113793381</v>
       </c>
     </row>
     <row r="202">
@@ -8523,13 +8523,13 @@
         <v>35</v>
       </c>
       <c r="B202" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C202" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D202" t="n">
-        <v>0.968763947128625</v>
+        <v>0.961149559386821</v>
       </c>
     </row>
     <row r="203">
@@ -8537,13 +8537,13 @@
         <v>35</v>
       </c>
       <c r="B203" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D203" t="n">
-        <v>0.965565752733948</v>
+        <v>0.960684400005902</v>
       </c>
     </row>
     <row r="204">
@@ -8551,13 +8551,13 @@
         <v>35</v>
       </c>
       <c r="B204" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C204" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D204" t="n">
-        <v>0.965469950957303</v>
+        <v>0.954614851595033</v>
       </c>
     </row>
     <row r="205">
@@ -8565,13 +8565,13 @@
         <v>35</v>
       </c>
       <c r="B205" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D205" t="n">
-        <v>0.963647450488854</v>
+        <v>0.95020473881332</v>
       </c>
     </row>
     <row r="206">
@@ -8579,13 +8579,13 @@
         <v>35</v>
       </c>
       <c r="B206" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C206" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D206" t="n">
-        <v>0.963014384073404</v>
+        <v>0.949997153516405</v>
       </c>
     </row>
     <row r="207">
@@ -8593,13 +8593,13 @@
         <v>35</v>
       </c>
       <c r="B207" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C207" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D207" t="n">
-        <v>0.962819882221282</v>
+        <v>0.94802097486045</v>
       </c>
     </row>
     <row r="208">
@@ -8607,13 +8607,13 @@
         <v>35</v>
       </c>
       <c r="B208" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C208" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D208" t="n">
-        <v>0.961627629233831</v>
+        <v>0.938367156074839</v>
       </c>
     </row>
     <row r="209">
@@ -8621,13 +8621,13 @@
         <v>35</v>
       </c>
       <c r="B209" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C209" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D209" t="n">
-        <v>0.961612844618915</v>
+        <v>0.937277956864382</v>
       </c>
     </row>
     <row r="210">
@@ -8635,13 +8635,13 @@
         <v>35</v>
       </c>
       <c r="B210" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C210" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D210" t="n">
-        <v>0.961244302263566</v>
+        <v>0.933016321229347</v>
       </c>
     </row>
     <row r="211">
@@ -8649,13 +8649,13 @@
         <v>35</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C211" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D211" t="n">
-        <v>0.955826451873771</v>
+        <v>0.928824287114907</v>
       </c>
     </row>
     <row r="212">
@@ -8663,13 +8663,13 @@
         <v>35</v>
       </c>
       <c r="B212" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C212" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D212" t="n">
-        <v>0.954873574910376</v>
+        <v>0.924359106723816</v>
       </c>
     </row>
     <row r="213">
@@ -8677,13 +8677,13 @@
         <v>35</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C213" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D213" t="n">
-        <v>0.952312456276701</v>
+        <v>0.924358119963249</v>
       </c>
     </row>
     <row r="214">
@@ -8691,13 +8691,13 @@
         <v>35</v>
       </c>
       <c r="B214" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C214" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D214" t="n">
-        <v>0.950930942993345</v>
+        <v>0.921940575904167</v>
       </c>
     </row>
     <row r="215">
@@ -8705,13 +8705,13 @@
         <v>35</v>
       </c>
       <c r="B215" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C215" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D215" t="n">
-        <v>0.950559763041546</v>
+        <v>0.920359913878469</v>
       </c>
     </row>
     <row r="216">
@@ -8719,13 +8719,13 @@
         <v>35</v>
       </c>
       <c r="B216" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C216" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D216" t="n">
-        <v>0.95039252975362</v>
+        <v>0.919886865677659</v>
       </c>
     </row>
     <row r="217">
@@ -8733,13 +8733,13 @@
         <v>35</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C217" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D217" t="n">
-        <v>0.946976813315906</v>
+        <v>0.918017904209724</v>
       </c>
     </row>
     <row r="218">
@@ -8750,10 +8750,10 @@
         <v>20</v>
       </c>
       <c r="C218" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D218" t="n">
-        <v>0.93426862136154</v>
+        <v>0.917403826440131</v>
       </c>
     </row>
     <row r="219">
@@ -8764,10 +8764,10 @@
         <v>17</v>
       </c>
       <c r="C219" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D219" t="n">
-        <v>0.93280575794989</v>
+        <v>0.916803381037648</v>
       </c>
     </row>
     <row r="220">
@@ -8775,13 +8775,13 @@
         <v>35</v>
       </c>
       <c r="B220" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C220" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D220" t="n">
-        <v>0.931028125859507</v>
+        <v>0.914094787389948</v>
       </c>
     </row>
     <row r="221">
@@ -8789,13 +8789,13 @@
         <v>35</v>
       </c>
       <c r="B221" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C221" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>0.930447205095344</v>
+        <v>0.913899431771741</v>
       </c>
     </row>
     <row r="222">
@@ -8803,13 +8803,13 @@
         <v>35</v>
       </c>
       <c r="B222" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C222" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D222" t="n">
-        <v>0.930185704153046</v>
+        <v>0.91383413199649</v>
       </c>
     </row>
     <row r="223">
@@ -8817,13 +8817,13 @@
         <v>35</v>
       </c>
       <c r="B223" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C223" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>0.928898807737566</v>
+        <v>0.911378489329231</v>
       </c>
     </row>
     <row r="224">
@@ -8831,13 +8831,13 @@
         <v>35</v>
       </c>
       <c r="B224" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D224" t="n">
-        <v>0.928468841238884</v>
+        <v>0.911064594242381</v>
       </c>
     </row>
     <row r="225">
@@ -8848,10 +8848,10 @@
         <v>21</v>
       </c>
       <c r="C225" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D225" t="n">
-        <v>0.92837769060537</v>
+        <v>0.909374188599145</v>
       </c>
     </row>
     <row r="226">
@@ -8859,13 +8859,13 @@
         <v>35</v>
       </c>
       <c r="B226" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C226" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>0.916982635151931</v>
+        <v>0.906451417770304</v>
       </c>
     </row>
     <row r="227">
@@ -8873,13 +8873,13 @@
         <v>35</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C227" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D227" t="n">
-        <v>0.916750745466097</v>
+        <v>0.905343336800658</v>
       </c>
     </row>
     <row r="228">
@@ -8887,13 +8887,13 @@
         <v>35</v>
       </c>
       <c r="B228" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C228" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>0.909683460663694</v>
+        <v>0.904884855411353</v>
       </c>
     </row>
     <row r="229">
@@ -8907,7 +8907,7 @@
         <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>0.909190176269385</v>
+        <v>0.90075390388753</v>
       </c>
     </row>
     <row r="230">
@@ -8915,13 +8915,13 @@
         <v>35</v>
       </c>
       <c r="B230" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C230" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D230" t="n">
-        <v>0.905418350694502</v>
+        <v>0.899532254133377</v>
       </c>
     </row>
     <row r="231">
@@ -8929,13 +8929,13 @@
         <v>35</v>
       </c>
       <c r="B231" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C231" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D231" t="n">
-        <v>0.90252242147675</v>
+        <v>0.890760796528991</v>
       </c>
     </row>
     <row r="232">
@@ -8943,13 +8943,13 @@
         <v>35</v>
       </c>
       <c r="B232" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C232" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D232" t="n">
-        <v>0.898361259133574</v>
+        <v>0.889093287316255</v>
       </c>
     </row>
     <row r="233">
@@ -8957,13 +8957,13 @@
         <v>35</v>
       </c>
       <c r="B233" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C233" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D233" t="n">
-        <v>0.897873073025394</v>
+        <v>0.882495375168733</v>
       </c>
     </row>
     <row r="234">
@@ -8971,13 +8971,13 @@
         <v>35</v>
       </c>
       <c r="B234" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D234" t="n">
-        <v>0.897243231866312</v>
+        <v>0.880535031102909</v>
       </c>
     </row>
     <row r="235">
@@ -8985,13 +8985,13 @@
         <v>35</v>
       </c>
       <c r="B235" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C235" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D235" t="n">
-        <v>0.895950220931004</v>
+        <v>0.878724933565797</v>
       </c>
     </row>
     <row r="236">
@@ -8999,13 +8999,13 @@
         <v>35</v>
       </c>
       <c r="B236" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C236" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D236" t="n">
-        <v>0.893602801024396</v>
+        <v>0.874696523896082</v>
       </c>
     </row>
     <row r="237">
@@ -9013,13 +9013,13 @@
         <v>35</v>
       </c>
       <c r="B237" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C237" t="s">
         <v>6</v>
       </c>
       <c r="D237" t="n">
-        <v>0.893468761522935</v>
+        <v>0.87464632322859</v>
       </c>
     </row>
     <row r="238">
@@ -9027,13 +9027,13 @@
         <v>35</v>
       </c>
       <c r="B238" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C238" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D238" t="n">
-        <v>0.891289892683328</v>
+        <v>0.871539870756924</v>
       </c>
     </row>
     <row r="239">
@@ -9044,10 +9044,10 @@
         <v>20</v>
       </c>
       <c r="C239" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D239" t="n">
-        <v>0.890896949024968</v>
+        <v>0.871080491389068</v>
       </c>
     </row>
     <row r="240">
@@ -9055,13 +9055,13 @@
         <v>35</v>
       </c>
       <c r="B240" t="s">
+        <v>16</v>
+      </c>
+      <c r="C240" t="s">
         <v>14</v>
       </c>
-      <c r="C240" t="s">
-        <v>6</v>
-      </c>
       <c r="D240" t="n">
-        <v>0.890699111717179</v>
+        <v>0.870890399818147</v>
       </c>
     </row>
     <row r="241">
@@ -9069,13 +9069,13 @@
         <v>35</v>
       </c>
       <c r="B241" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C241" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>0.887924976835861</v>
+        <v>0.869907648828893</v>
       </c>
     </row>
     <row r="242">
@@ -9083,13 +9083,13 @@
         <v>35</v>
       </c>
       <c r="B242" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C242" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D242" t="n">
-        <v>0.887361502241587</v>
+        <v>0.869427442996106</v>
       </c>
     </row>
     <row r="243">
@@ -9100,10 +9100,10 @@
         <v>16</v>
       </c>
       <c r="C243" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D243" t="n">
-        <v>0.887087584475339</v>
+        <v>0.867658116203645</v>
       </c>
     </row>
     <row r="244">
@@ -9111,13 +9111,13 @@
         <v>35</v>
       </c>
       <c r="B244" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C244" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D244" t="n">
-        <v>0.884535098328299</v>
+        <v>0.867191482482115</v>
       </c>
     </row>
     <row r="245">
@@ -9125,13 +9125,13 @@
         <v>35</v>
       </c>
       <c r="B245" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C245" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>0.883905818108557</v>
+        <v>0.866814220997126</v>
       </c>
     </row>
     <row r="246">
@@ -9139,13 +9139,13 @@
         <v>35</v>
       </c>
       <c r="B246" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C246" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D246" t="n">
-        <v>0.883812602387531</v>
+        <v>0.866711868051337</v>
       </c>
     </row>
     <row r="247">
@@ -9153,13 +9153,13 @@
         <v>35</v>
       </c>
       <c r="B247" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C247" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D247" t="n">
-        <v>0.883665968650807</v>
+        <v>0.86567297137302</v>
       </c>
     </row>
     <row r="248">
@@ -9167,13 +9167,13 @@
         <v>35</v>
       </c>
       <c r="B248" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C248" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D248" t="n">
-        <v>0.882313818475489</v>
+        <v>0.863937200052375</v>
       </c>
     </row>
     <row r="249">
@@ -9181,13 +9181,13 @@
         <v>35</v>
       </c>
       <c r="B249" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C249" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D249" t="n">
-        <v>0.878774048043518</v>
+        <v>0.859921293983131</v>
       </c>
     </row>
     <row r="250">
@@ -9195,13 +9195,13 @@
         <v>35</v>
       </c>
       <c r="B250" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C250" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D250" t="n">
-        <v>0.878648748995595</v>
+        <v>0.858195442969367</v>
       </c>
     </row>
     <row r="251">
@@ -9209,13 +9209,13 @@
         <v>35</v>
       </c>
       <c r="B251" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C251" t="s">
         <v>8</v>
       </c>
       <c r="D251" t="n">
-        <v>0.877636498151588</v>
+        <v>0.857100390590523</v>
       </c>
     </row>
     <row r="252">
@@ -9223,13 +9223,13 @@
         <v>35</v>
       </c>
       <c r="B252" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C252" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D252" t="n">
-        <v>0.87721870532225</v>
+        <v>0.854417287659182</v>
       </c>
     </row>
     <row r="253">
@@ -9237,13 +9237,13 @@
         <v>35</v>
       </c>
       <c r="B253" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C253" t="s">
         <v>13</v>
       </c>
       <c r="D253" t="n">
-        <v>0.876021321496337</v>
+        <v>0.85441669950153</v>
       </c>
     </row>
     <row r="254">
@@ -9251,13 +9251,13 @@
         <v>35</v>
       </c>
       <c r="B254" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C254" t="s">
         <v>8</v>
       </c>
       <c r="D254" t="n">
-        <v>0.875954246313607</v>
+        <v>0.85394077384708</v>
       </c>
     </row>
     <row r="255">
@@ -9265,13 +9265,13 @@
         <v>35</v>
       </c>
       <c r="B255" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C255" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D255" t="n">
-        <v>0.875409906565435</v>
+        <v>0.853616585302679</v>
       </c>
     </row>
     <row r="256">
@@ -9279,13 +9279,13 @@
         <v>35</v>
       </c>
       <c r="B256" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C256" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D256" t="n">
-        <v>0.871799748073203</v>
+        <v>0.852822093596291</v>
       </c>
     </row>
     <row r="257">
@@ -9299,7 +9299,7 @@
         <v>12</v>
       </c>
       <c r="D257" t="n">
-        <v>0.870143101861005</v>
+        <v>0.851264325515118</v>
       </c>
     </row>
     <row r="258">
@@ -9310,10 +9310,10 @@
         <v>17</v>
       </c>
       <c r="C258" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D258" t="n">
-        <v>0.852210402427954</v>
+        <v>0.849877794807057</v>
       </c>
     </row>
     <row r="259">
@@ -9321,13 +9321,13 @@
         <v>35</v>
       </c>
       <c r="B259" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C259" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D259" t="n">
-        <v>0.849995344271259</v>
+        <v>0.847057613244987</v>
       </c>
     </row>
     <row r="260">
@@ -9338,10 +9338,10 @@
         <v>21</v>
       </c>
       <c r="C260" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D260" t="n">
-        <v>0.846636260534143</v>
+        <v>0.845913741158481</v>
       </c>
     </row>
     <row r="261">
@@ -9352,10 +9352,10 @@
         <v>21</v>
       </c>
       <c r="C261" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D261" t="n">
-        <v>0.844890392784049</v>
+        <v>0.841545154150101</v>
       </c>
     </row>
     <row r="262">
@@ -9363,13 +9363,13 @@
         <v>35</v>
       </c>
       <c r="B262" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C262" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D262" t="n">
-        <v>0.837281319176401</v>
+        <v>0.818919156583693</v>
       </c>
     </row>
     <row r="263">
@@ -9377,13 +9377,13 @@
         <v>35</v>
       </c>
       <c r="B263" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C263" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D263" t="n">
-        <v>0.834859059186078</v>
+        <v>0.818611491686996</v>
       </c>
     </row>
     <row r="264">
@@ -9391,13 +9391,13 @@
         <v>35</v>
       </c>
       <c r="B264" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C264" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D264" t="n">
-        <v>0.83177531747668</v>
+        <v>0.807190287395928</v>
       </c>
     </row>
     <row r="265">
@@ -9408,10 +9408,10 @@
         <v>21</v>
       </c>
       <c r="C265" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D265" t="n">
-        <v>0.829653902791547</v>
+        <v>0.805738212886765</v>
       </c>
     </row>
   </sheetData>
@@ -9444,189 +9444,189 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="D2" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="E2" t="n">
-        <v>0.805</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.72</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D4" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.68</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="D6" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="E6" t="n">
-        <v>0.745</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="D7" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="E7" t="n">
-        <v>0.75</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.65</v>
+        <v>0.47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.68</v>
+        <v>0.565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.68</v>
+        <v>0.49</v>
       </c>
       <c r="E10" t="n">
-        <v>0.785</v>
+        <v>0.565</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="D11" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.715</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="D12" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="E12" t="n">
-        <v>0.74</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="13">
@@ -9637,13 +9637,13 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="E13" t="n">
-        <v>0.705</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="14">
@@ -9654,47 +9654,47 @@
         <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="D14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="E14" t="n">
-        <v>0.83</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="D15" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.765</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="D16" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>0.75</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="17">
@@ -9708,15 +9708,15 @@
         <v>0.7</v>
       </c>
       <c r="D17" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="E17" t="n">
-        <v>0.745</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -9725,15 +9725,15 @@
         <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="E18" t="n">
-        <v>0.755</v>
+        <v>0.685</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -9742,134 +9742,134 @@
         <v>0.68</v>
       </c>
       <c r="D19" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="E19" t="n">
-        <v>0.79</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="E20" t="n">
-        <v>0.785</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="D21" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="E21" t="n">
-        <v>0.75</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="D22" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="E22" t="n">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="E23" t="n">
-        <v>0.83</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
       </c>
       <c r="C24" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D24" t="n">
         <v>0.62</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.77</v>
-      </c>
       <c r="E24" t="n">
-        <v>0.785</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="D25" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.775</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
       <c r="C26" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.84</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.83</v>
-      </c>
       <c r="E26" t="n">
-        <v>0.875</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -9878,15 +9878,15 @@
         <v>0.84</v>
       </c>
       <c r="D27" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="E27" t="n">
-        <v>0.83</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -9895,32 +9895,32 @@
         <v>0.84</v>
       </c>
       <c r="D28" t="n">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
       <c r="E28" t="n">
-        <v>0.84</v>
+        <v>0.815</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="D29" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.825</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -9932,29 +9932,29 @@
         <v>0.85</v>
       </c>
       <c r="E30" t="n">
-        <v>0.875</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="E31" t="n">
-        <v>0.875</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>34</v>
@@ -9963,15 +9963,15 @@
         <v>0.8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="E32" t="n">
-        <v>0.855</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -9980,214 +9980,214 @@
         <v>0.8</v>
       </c>
       <c r="D33" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="E33" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="D34" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="E34" t="n">
-        <v>0.875</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="D35" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="E35" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="D36" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="E36" t="n">
-        <v>0.885</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="D37" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="E37" t="n">
-        <v>0.875</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
         <v>35</v>
       </c>
       <c r="C38" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="D38" t="n">
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="E38" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="D39" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="E39" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.81</v>
+        <v>0.7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.865</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="D41" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="E41" t="n">
-        <v>0.845</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
       </c>
       <c r="C42" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="E42" t="n">
-        <v>0.825</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
         <v>35</v>
       </c>
       <c r="C43" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="D43" t="n">
-        <v>0.83</v>
+        <v>0.69</v>
       </c>
       <c r="E43" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
         <v>35</v>
       </c>
       <c r="C44" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="D44" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="E44" t="n">
-        <v>0.875</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
         <v>35</v>
       </c>
       <c r="C45" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="D45" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="E45" t="n">
-        <v>0.815</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="46">
@@ -10198,64 +10198,64 @@
         <v>35</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="D46" t="n">
-        <v>0.79</v>
+        <v>0.69</v>
       </c>
       <c r="E46" t="n">
-        <v>0.85</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
         <v>35</v>
       </c>
       <c r="C47" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="D47" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="E47" t="n">
-        <v>0.83</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
         <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="D48" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="E48" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
         <v>35</v>
       </c>
       <c r="C49" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="E49" t="n">
-        <v>0.815</v>
+        <v>0.69</v>
       </c>
     </row>
   </sheetData>
